--- a/temelozet.xlsx
+++ b/temelozet.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\indikatör\BİST TARAMA BOTU\bist-tarama-botu-main\bist-tarama-botu-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8688"/>
   </bookViews>
   <sheets>
-    <sheet name="isyatirim" sheetId="1" r:id="R58864d040e1e4d9e"/>
+    <sheet name="isyatirim" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="1239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1242">
   <si>
     <t>Kod</t>
   </si>
@@ -3728,17 +3736,38 @@
   </si>
   <si>
     <t>Şok Marketler</t>
+  </si>
+  <si>
+    <t>DOFRB</t>
+  </si>
+  <si>
+    <t>Dof Robotik Sanayi A.Ş.</t>
+  </si>
+  <si>
+    <t>Endüstriyel Makine / Teknoloji</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3759,25 +3788,306 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H591"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I599"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3803,7 +4113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -3829,7 +4139,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3855,7 +4165,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -3881,7 +4191,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -3907,7 +4217,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -3930,10 +4240,10 @@
         <v>27.6</v>
       </c>
       <c r="H6" s="1">
-        <v>259.9</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>259.89999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -3959,7 +4269,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -3973,7 +4283,7 @@
         <v>27.98</v>
       </c>
       <c r="E8" s="1">
-        <v>8217.7</v>
+        <v>8217.7000000000007</v>
       </c>
       <c r="F8" s="1">
         <v>210</v>
@@ -3985,7 +4295,7 @@
         <v>293.7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -4002,7 +4312,7 @@
         <v>5172</v>
       </c>
       <c r="F9" s="1">
-        <v>132.2</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="G9" s="1">
         <v>48.6</v>
@@ -4011,7 +4321,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -4022,7 +4332,7 @@
         <v>33</v>
       </c>
       <c r="D10" s="1">
-        <v>137.3</v>
+        <v>137.30000000000001</v>
       </c>
       <c r="E10" s="1">
         <v>24714</v>
@@ -4031,13 +4341,13 @@
         <v>631.6</v>
       </c>
       <c r="G10" s="1">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H10" s="1">
         <v>180</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -4063,7 +4373,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -4089,7 +4399,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -4115,7 +4425,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
@@ -4141,7 +4451,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -4167,7 +4477,7 @@
         <v>248.2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
@@ -4193,7 +4503,7 @@
         <v>729.2</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -4219,7 +4529,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -4245,7 +4555,7 @@
         <v>636.6</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
@@ -4271,7 +4581,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
@@ -4297,7 +4607,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -4320,10 +4630,10 @@
         <v>9.9</v>
       </c>
       <c r="H21" s="1">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
@@ -4343,13 +4653,13 @@
         <v>933.3</v>
       </c>
       <c r="G22" s="1">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="H22" s="1">
         <v>3885</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>64</v>
       </c>
@@ -4360,22 +4670,22 @@
         <v>49</v>
       </c>
       <c r="D23" s="1">
-        <v>33.34</v>
+        <v>33.340000000000003</v>
       </c>
       <c r="E23" s="1">
         <v>40886.1</v>
       </c>
       <c r="F23" s="1">
-        <v>1044.9</v>
+        <v>1044.9000000000001</v>
       </c>
       <c r="G23" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H23" s="1">
         <v>1226.3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -4401,7 +4711,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>68</v>
       </c>
@@ -4427,7 +4737,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
@@ -4438,7 +4748,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="1">
-        <v>150.7</v>
+        <v>150.69999999999999</v>
       </c>
       <c r="E26" s="1">
         <v>28851.1</v>
@@ -4453,7 +4763,7 @@
         <v>191.4</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -4479,7 +4789,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -4493,7 +4803,7 @@
         <v>883.5</v>
       </c>
       <c r="E28" s="1">
-        <v>9541.8</v>
+        <v>9541.7999999999993</v>
       </c>
       <c r="F28" s="1">
         <v>243.9</v>
@@ -4505,7 +4815,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
@@ -4531,7 +4841,7 @@
         <v>289.8</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>80</v>
       </c>
@@ -4545,7 +4855,7 @@
         <v>83.55</v>
       </c>
       <c r="E30" s="1">
-        <v>36344.3</v>
+        <v>36344.300000000003</v>
       </c>
       <c r="F30" s="1">
         <v>928.9</v>
@@ -4557,7 +4867,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -4577,13 +4887,13 @@
         <v>450.4</v>
       </c>
       <c r="G31" s="1">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="H31" s="1">
         <v>2500</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>84</v>
       </c>
@@ -4606,10 +4916,10 @@
         <v>35</v>
       </c>
       <c r="H32" s="1">
-        <v>38.7</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
@@ -4635,7 +4945,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>89</v>
       </c>
@@ -4661,7 +4971,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>91</v>
       </c>
@@ -4675,19 +4985,19 @@
         <v>6.94</v>
       </c>
       <c r="E35" s="1">
-        <v>5100.9</v>
+        <v>5100.8999999999996</v>
       </c>
       <c r="F35" s="1">
         <v>130.4</v>
       </c>
       <c r="G35" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H35" s="1">
         <v>735</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
@@ -4701,7 +5011,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="1">
-        <v>18117.6</v>
+        <v>18117.599999999999</v>
       </c>
       <c r="F36" s="1">
         <v>463</v>
@@ -4713,7 +5023,7 @@
         <v>235.3</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>97</v>
       </c>
@@ -4739,7 +5049,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
@@ -4765,7 +5075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>103</v>
       </c>
@@ -4791,7 +5101,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>106</v>
       </c>
@@ -4811,13 +5121,13 @@
         <v>2173</v>
       </c>
       <c r="G40" s="1">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H40" s="1">
         <v>592.1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>109</v>
       </c>
@@ -4843,7 +5153,7 @@
         <v>243.5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
@@ -4854,7 +5164,7 @@
         <v>33</v>
       </c>
       <c r="D42" s="1">
-        <v>73.4</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="E42" s="1">
         <v>31562</v>
@@ -4869,7 +5179,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>113</v>
       </c>
@@ -4895,7 +5205,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>116</v>
       </c>
@@ -4915,13 +5225,13 @@
         <v>1074.7</v>
       </c>
       <c r="G44" s="1">
-        <v>34.7</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="H44" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>118</v>
       </c>
@@ -4947,7 +5257,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>121</v>
       </c>
@@ -4973,7 +5283,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>124</v>
       </c>
@@ -4999,7 +5309,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
@@ -5025,7 +5335,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>130</v>
       </c>
@@ -5039,19 +5349,19 @@
         <v>36.1</v>
       </c>
       <c r="E49" s="1">
-        <v>9529.7</v>
+        <v>9529.7000000000007</v>
       </c>
       <c r="F49" s="1">
         <v>243.6</v>
       </c>
       <c r="G49" s="1">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H49" s="1">
         <v>264</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>132</v>
       </c>
@@ -5077,7 +5387,7 @@
         <v>204.4</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>134</v>
       </c>
@@ -5103,7 +5413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>136</v>
       </c>
@@ -5129,7 +5439,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>138</v>
       </c>
@@ -5143,7 +5453,7 @@
         <v>110.3</v>
       </c>
       <c r="E53" s="1">
-        <v>74532.8</v>
+        <v>74532.800000000003</v>
       </c>
       <c r="F53" s="1">
         <v>1904.9</v>
@@ -5155,7 +5465,7 @@
         <v>675.7</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>140</v>
       </c>
@@ -5181,7 +5491,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>142</v>
       </c>
@@ -5192,7 +5502,7 @@
         <v>96</v>
       </c>
       <c r="D55" s="1">
-        <v>134.7</v>
+        <v>134.69999999999999</v>
       </c>
       <c r="E55" s="1">
         <v>614232</v>
@@ -5207,7 +5517,7 @@
         <v>4560</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>144</v>
       </c>
@@ -5233,7 +5543,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>146</v>
       </c>
@@ -5259,7 +5569,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>148</v>
       </c>
@@ -5282,10 +5592,10 @@
         <v>20.3</v>
       </c>
       <c r="H58" s="1">
-        <v>138.8</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>138.80000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>150</v>
       </c>
@@ -5311,7 +5621,7 @@
         <v>263.3</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>152</v>
       </c>
@@ -5337,7 +5647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>154</v>
       </c>
@@ -5354,7 +5664,7 @@
         <v>321</v>
       </c>
       <c r="F61" s="1">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G61" s="1">
         <v>99.8</v>
@@ -5363,7 +5673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>157</v>
       </c>
@@ -5389,7 +5699,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>159</v>
       </c>
@@ -5415,7 +5725,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>161</v>
       </c>
@@ -5441,7 +5751,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>163</v>
       </c>
@@ -5467,7 +5777,7 @@
         <v>111.6</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>165</v>
       </c>
@@ -5484,16 +5794,16 @@
         <v>1554.1</v>
       </c>
       <c r="F66" s="1">
-        <v>39.7</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="G66" s="1">
         <v>63.3</v>
       </c>
       <c r="H66" s="1">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>167</v>
       </c>
@@ -5519,7 +5829,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>169</v>
       </c>
@@ -5530,22 +5840,22 @@
         <v>49</v>
       </c>
       <c r="D68" s="1">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E68" s="1">
         <v>11703</v>
       </c>
       <c r="F68" s="1">
-        <v>299.1</v>
+        <v>299.10000000000002</v>
       </c>
       <c r="G68" s="1">
-        <v>18.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H68" s="1">
         <v>705</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>171</v>
       </c>
@@ -5565,13 +5875,13 @@
         <v>175.2</v>
       </c>
       <c r="G69" s="1">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H69" s="1">
         <v>277.5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>173</v>
       </c>
@@ -5597,7 +5907,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>175</v>
       </c>
@@ -5611,7 +5921,7 @@
         <v>128.5</v>
       </c>
       <c r="E71" s="1">
-        <v>28244.4</v>
+        <v>28244.400000000001</v>
       </c>
       <c r="F71" s="1">
         <v>721.8</v>
@@ -5623,7 +5933,7 @@
         <v>219.8</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>178</v>
       </c>
@@ -5649,7 +5959,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>180</v>
       </c>
@@ -5675,7 +5985,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>182</v>
       </c>
@@ -5701,7 +6011,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>184</v>
       </c>
@@ -5718,7 +6028,7 @@
         <v>680</v>
       </c>
       <c r="F75" s="1">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G75" s="1">
         <v>97.2</v>
@@ -5727,7 +6037,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>187</v>
       </c>
@@ -5738,7 +6048,7 @@
         <v>99</v>
       </c>
       <c r="D76" s="1">
-        <v>19.49</v>
+        <v>19.489999999999998</v>
       </c>
       <c r="E76" s="1">
         <v>21672.9</v>
@@ -5753,7 +6063,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>189</v>
       </c>
@@ -5779,7 +6089,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>192</v>
       </c>
@@ -5796,7 +6106,7 @@
         <v>1574.6</v>
       </c>
       <c r="F78" s="1">
-        <v>40.2</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="G78" s="1">
         <v>58.7</v>
@@ -5805,7 +6115,7 @@
         <v>241.9</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>194</v>
       </c>
@@ -5819,19 +6129,19 @@
         <v>196</v>
       </c>
       <c r="E79" s="1">
-        <v>19604.6</v>
+        <v>19604.599999999999</v>
       </c>
       <c r="F79" s="1">
         <v>501</v>
       </c>
       <c r="G79" s="1">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H79" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>197</v>
       </c>
@@ -5842,10 +6152,10 @@
         <v>93</v>
       </c>
       <c r="D80" s="1">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="E80" s="1">
-        <v>4549.1</v>
+        <v>4549.1000000000004</v>
       </c>
       <c r="F80" s="1">
         <v>116.3</v>
@@ -5857,7 +6167,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>199</v>
       </c>
@@ -5868,7 +6178,7 @@
         <v>25</v>
       </c>
       <c r="D81" s="1">
-        <v>8.22</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="E81" s="1">
         <v>6699.3</v>
@@ -5883,7 +6193,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>201</v>
       </c>
@@ -5909,7 +6219,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>203</v>
       </c>
@@ -5935,7 +6245,7 @@
         <v>5580</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>205</v>
       </c>
@@ -5961,7 +6271,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>207</v>
       </c>
@@ -5987,7 +6297,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>209</v>
       </c>
@@ -6013,7 +6323,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>211</v>
       </c>
@@ -6039,7 +6349,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>213</v>
       </c>
@@ -6065,7 +6375,7 @@
         <v>683.2</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>215</v>
       </c>
@@ -6082,7 +6392,7 @@
         <v>661.8</v>
       </c>
       <c r="F89" s="1">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G89" s="1">
         <v>66.8</v>
@@ -6091,7 +6401,7 @@
         <v>93.6</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>217</v>
       </c>
@@ -6117,7 +6427,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>219</v>
       </c>
@@ -6131,7 +6441,7 @@
         <v>21.58</v>
       </c>
       <c r="E91" s="1">
-        <v>2151.3</v>
+        <v>2151.3000000000002</v>
       </c>
       <c r="F91" s="1">
         <v>55</v>
@@ -6143,7 +6453,7 @@
         <v>99.7</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>222</v>
       </c>
@@ -6166,10 +6476,10 @@
         <v>29.9</v>
       </c>
       <c r="H92" s="1">
-        <v>4364.6</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>4364.6000000000004</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>225</v>
       </c>
@@ -6195,7 +6505,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>228</v>
       </c>
@@ -6206,7 +6516,7 @@
         <v>99</v>
       </c>
       <c r="D94" s="1">
-        <v>35.88</v>
+        <v>35.880000000000003</v>
       </c>
       <c r="E94" s="1">
         <v>3839.2</v>
@@ -6221,7 +6531,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>230</v>
       </c>
@@ -6247,7 +6557,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>232</v>
       </c>
@@ -6273,7 +6583,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>235</v>
       </c>
@@ -6299,7 +6609,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>237</v>
       </c>
@@ -6316,16 +6626,16 @@
         <v>10100</v>
       </c>
       <c r="F98" s="1">
-        <v>258.1</v>
+        <v>258.10000000000002</v>
       </c>
       <c r="G98" s="1">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="H98" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>239</v>
       </c>
@@ -6351,7 +6661,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>241</v>
       </c>
@@ -6377,7 +6687,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
@@ -6403,7 +6713,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>245</v>
       </c>
@@ -6417,7 +6727,7 @@
         <v>15.03</v>
       </c>
       <c r="E102" s="1">
-        <v>8672.3</v>
+        <v>8672.2999999999993</v>
       </c>
       <c r="F102" s="1">
         <v>221.6</v>
@@ -6429,7 +6739,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>247</v>
       </c>
@@ -6455,7 +6765,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>249</v>
       </c>
@@ -6475,13 +6785,13 @@
         <v>49.9</v>
       </c>
       <c r="G104" s="1">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="H104" s="1">
         <v>80.5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>251</v>
       </c>
@@ -6507,7 +6817,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>254</v>
       </c>
@@ -6533,7 +6843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>256</v>
       </c>
@@ -6547,7 +6857,7 @@
         <v>20.66</v>
       </c>
       <c r="E107" s="1">
-        <v>4958.4</v>
+        <v>4958.3999999999996</v>
       </c>
       <c r="F107" s="1">
         <v>126.7</v>
@@ -6559,7 +6869,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>258</v>
       </c>
@@ -6585,7 +6895,7 @@
         <v>168.7</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>260</v>
       </c>
@@ -6608,10 +6918,10 @@
         <v>19.7</v>
       </c>
       <c r="H109" s="1">
-        <v>141.8</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>141.80000000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>263</v>
       </c>
@@ -6637,7 +6947,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>265</v>
       </c>
@@ -6663,7 +6973,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>267</v>
       </c>
@@ -6689,7 +6999,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>269</v>
       </c>
@@ -6715,7 +7025,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>271</v>
       </c>
@@ -6729,19 +7039,19 @@
         <v>73.75</v>
       </c>
       <c r="E114" s="1">
-        <v>22502.4</v>
+        <v>22502.400000000001</v>
       </c>
       <c r="F114" s="1">
         <v>575.1</v>
       </c>
       <c r="G114" s="1">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H114" s="1">
-        <v>305.1</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>305.10000000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>274</v>
       </c>
@@ -6767,7 +7077,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>276</v>
       </c>
@@ -6793,7 +7103,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>278</v>
       </c>
@@ -6810,7 +7120,7 @@
         <v>1434.6</v>
       </c>
       <c r="F117" s="1">
-        <v>36.7</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="G117" s="1">
         <v>52.7</v>
@@ -6819,7 +7129,7 @@
         <v>84.2</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>280</v>
       </c>
@@ -6845,7 +7155,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>282</v>
       </c>
@@ -6871,7 +7181,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>284</v>
       </c>
@@ -6885,7 +7195,7 @@
         <v>75.55</v>
       </c>
       <c r="E120" s="1">
-        <v>9653.3</v>
+        <v>9653.2999999999993</v>
       </c>
       <c r="F120" s="1">
         <v>246.7</v>
@@ -6897,7 +7207,7 @@
         <v>127.8</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>286</v>
       </c>
@@ -6920,10 +7230,10 @@
         <v>98.4</v>
       </c>
       <c r="H121" s="1">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>288</v>
       </c>
@@ -6949,7 +7259,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>290</v>
       </c>
@@ -6975,7 +7285,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>293</v>
       </c>
@@ -6989,7 +7299,7 @@
         <v>52.95</v>
       </c>
       <c r="E124" s="1">
-        <v>148158.3</v>
+        <v>148158.29999999999</v>
       </c>
       <c r="F124" s="1">
         <v>3786.5</v>
@@ -7001,7 +7311,7 @@
         <v>2798.1</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>295</v>
       </c>
@@ -7027,7 +7337,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>297</v>
       </c>
@@ -7053,7 +7363,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>299</v>
       </c>
@@ -7079,7 +7389,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>302</v>
       </c>
@@ -7105,7 +7415,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>305</v>
       </c>
@@ -7131,7 +7441,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>307</v>
       </c>
@@ -7157,7 +7467,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>309</v>
       </c>
@@ -7174,7 +7484,7 @@
         <v>2970</v>
       </c>
       <c r="F131" s="1">
-        <v>75.9</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="G131" s="1">
         <v>53.8</v>
@@ -7183,7 +7493,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>311</v>
       </c>
@@ -7209,7 +7519,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>313</v>
       </c>
@@ -7235,7 +7545,7 @@
         <v>2344.4</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>315</v>
       </c>
@@ -7255,13 +7565,13 @@
         <v>48</v>
       </c>
       <c r="G134" s="1">
-        <v>40.7</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="H134" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>317</v>
       </c>
@@ -7275,7 +7585,7 @@
         <v>39.92</v>
       </c>
       <c r="E135" s="1">
-        <v>5189.6</v>
+        <v>5189.6000000000004</v>
       </c>
       <c r="F135" s="1">
         <v>132.6</v>
@@ -7287,7 +7597,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>319</v>
       </c>
@@ -7304,7 +7614,7 @@
         <v>1398</v>
       </c>
       <c r="F136" s="1">
-        <v>35.7</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="G136" s="1">
         <v>51.7</v>
@@ -7313,7 +7623,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>321</v>
       </c>
@@ -7339,7 +7649,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>323</v>
       </c>
@@ -7365,7 +7675,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>325</v>
       </c>
@@ -7376,7 +7686,7 @@
         <v>327</v>
       </c>
       <c r="D139" s="1">
-        <v>38.62</v>
+        <v>38.619999999999997</v>
       </c>
       <c r="E139" s="1">
         <v>2085.5</v>
@@ -7391,7 +7701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>328</v>
       </c>
@@ -7405,7 +7715,7 @@
         <v>48.64</v>
       </c>
       <c r="E140" s="1">
-        <v>9595.8</v>
+        <v>9595.7999999999993</v>
       </c>
       <c r="F140" s="1">
         <v>245.2</v>
@@ -7417,7 +7727,7 @@
         <v>197.3</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>330</v>
       </c>
@@ -7428,7 +7738,7 @@
         <v>327</v>
       </c>
       <c r="D141" s="1">
-        <v>9.63</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="E141" s="1">
         <v>4718.7</v>
@@ -7443,7 +7753,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>332</v>
       </c>
@@ -7457,7 +7767,7 @@
         <v>47.7</v>
       </c>
       <c r="E142" s="1">
-        <v>1097.1</v>
+        <v>1097.0999999999999</v>
       </c>
       <c r="F142" s="1">
         <v>28</v>
@@ -7469,7 +7779,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>334</v>
       </c>
@@ -7486,7 +7796,7 @@
         <v>93916.7</v>
       </c>
       <c r="F143" s="1">
-        <v>2400.2</v>
+        <v>2400.1999999999998</v>
       </c>
       <c r="G143" s="1">
         <v>25</v>
@@ -7495,7 +7805,7 @@
         <v>333.3</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>336</v>
       </c>
@@ -7512,7 +7822,7 @@
         <v>11361.1</v>
       </c>
       <c r="F144" s="1">
-        <v>290.4</v>
+        <v>290.39999999999998</v>
       </c>
       <c r="G144" s="1">
         <v>17.7</v>
@@ -7521,7 +7831,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>338</v>
       </c>
@@ -7547,7 +7857,7 @@
         <v>119.7</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>340</v>
       </c>
@@ -7573,7 +7883,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>342</v>
       </c>
@@ -7599,7 +7909,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>344</v>
       </c>
@@ -7613,7 +7923,7 @@
         <v>25.86</v>
       </c>
       <c r="E148" s="1">
-        <v>4791.9</v>
+        <v>4791.8999999999996</v>
       </c>
       <c r="F148" s="1">
         <v>122.5</v>
@@ -7625,7 +7935,7 @@
         <v>185.3</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>346</v>
       </c>
@@ -7639,7 +7949,7 @@
         <v>7825</v>
       </c>
       <c r="E149" s="1">
-        <v>85945.6</v>
+        <v>85945.600000000006</v>
       </c>
       <c r="F149" s="1">
         <v>2196.5</v>
@@ -7651,7 +7961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>348</v>
       </c>
@@ -7677,7 +7987,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>350</v>
       </c>
@@ -7700,10 +8010,10 @@
         <v>30</v>
       </c>
       <c r="H151" s="1">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>352</v>
       </c>
@@ -7717,19 +8027,19 @@
         <v>15.11</v>
       </c>
       <c r="E152" s="1">
-        <v>39542.8</v>
+        <v>39542.800000000003</v>
       </c>
       <c r="F152" s="1">
         <v>1010.6</v>
       </c>
       <c r="G152" s="1">
-        <v>35.7</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="H152" s="1">
         <v>2617</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>354</v>
       </c>
@@ -7755,7 +8065,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>357</v>
       </c>
@@ -7781,7 +8091,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>359</v>
       </c>
@@ -7807,7 +8117,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>361</v>
       </c>
@@ -7833,7 +8143,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>363</v>
       </c>
@@ -7859,7 +8169,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>365</v>
       </c>
@@ -7879,13 +8189,13 @@
         <v>40</v>
       </c>
       <c r="G158" s="1">
-        <v>32.3</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H158" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>367</v>
       </c>
@@ -7911,7 +8221,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>369</v>
       </c>
@@ -7937,7 +8247,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>372</v>
       </c>
@@ -7963,7 +8273,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>374</v>
       </c>
@@ -7989,7 +8299,7 @@
         <v>402.2</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>376</v>
       </c>
@@ -8015,7 +8325,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>378</v>
       </c>
@@ -8029,7 +8339,7 @@
         <v>46.84</v>
       </c>
       <c r="E164" s="1">
-        <v>32097.6</v>
+        <v>32097.599999999999</v>
       </c>
       <c r="F164" s="1">
         <v>820.3</v>
@@ -8041,7 +8351,7 @@
         <v>685.3</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>380</v>
       </c>
@@ -8067,7 +8377,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>382</v>
       </c>
@@ -8093,7 +8403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>384</v>
       </c>
@@ -8119,7 +8429,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>386</v>
       </c>
@@ -8145,7 +8455,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>388</v>
       </c>
@@ -8171,7 +8481,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>390</v>
       </c>
@@ -8188,7 +8498,7 @@
         <v>10801.9</v>
       </c>
       <c r="F170" s="1">
-        <v>276.1</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="G170" s="1">
         <v>13.1</v>
@@ -8197,7 +8507,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>392</v>
       </c>
@@ -8211,19 +8521,19 @@
         <v>3.06</v>
       </c>
       <c r="E171" s="1">
-        <v>2203.2</v>
+        <v>2203.1999999999998</v>
       </c>
       <c r="F171" s="1">
         <v>56.3</v>
       </c>
       <c r="G171" s="1">
-        <v>34.3</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="H171" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>394</v>
       </c>
@@ -8249,7 +8559,7 @@
         <v>190.6</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>396</v>
       </c>
@@ -8275,7 +8585,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>398</v>
       </c>
@@ -8301,7 +8611,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>400</v>
       </c>
@@ -8324,10 +8634,10 @@
         <v>62.9</v>
       </c>
       <c r="H175" s="1">
-        <v>9.3</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>402</v>
       </c>
@@ -8353,7 +8663,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>405</v>
       </c>
@@ -8379,7 +8689,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>407</v>
       </c>
@@ -8393,7 +8703,7 @@
         <v>36.4</v>
       </c>
       <c r="E178" s="1">
-        <v>4717.4</v>
+        <v>4717.3999999999996</v>
       </c>
       <c r="F178" s="1">
         <v>120.6</v>
@@ -8405,7 +8715,7 @@
         <v>129.6</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>409</v>
       </c>
@@ -8416,7 +8726,7 @@
         <v>10</v>
       </c>
       <c r="D179" s="1">
-        <v>34.16</v>
+        <v>34.159999999999997</v>
       </c>
       <c r="E179" s="1">
         <v>5124</v>
@@ -8425,13 +8735,13 @@
         <v>131</v>
       </c>
       <c r="G179" s="1">
-        <v>80.6</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="H179" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>411</v>
       </c>
@@ -8457,7 +8767,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>413</v>
       </c>
@@ -8483,7 +8793,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>415</v>
       </c>
@@ -8509,7 +8819,7 @@
         <v>437.2</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>417</v>
       </c>
@@ -8532,10 +8842,10 @@
         <v>20</v>
       </c>
       <c r="H183" s="1">
-        <v>1181.1</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>1181.0999999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>419</v>
       </c>
@@ -8552,7 +8862,7 @@
         <v>48600</v>
       </c>
       <c r="F184" s="1">
-        <v>1242.1</v>
+        <v>1242.0999999999999</v>
       </c>
       <c r="G184" s="1">
         <v>22</v>
@@ -8561,7 +8871,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>421</v>
       </c>
@@ -8581,13 +8891,13 @@
         <v>9722</v>
       </c>
       <c r="G185" s="1">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H185" s="1">
         <v>6000</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>423</v>
       </c>
@@ -8613,7 +8923,7 @@
         <v>116.8</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>425</v>
       </c>
@@ -8630,7 +8940,7 @@
         <v>2890</v>
       </c>
       <c r="F187" s="1">
-        <v>73.9</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="G187" s="1">
         <v>58.2</v>
@@ -8639,7 +8949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>427</v>
       </c>
@@ -8656,7 +8966,7 @@
         <v>5525.6</v>
       </c>
       <c r="F188" s="1">
-        <v>141.2</v>
+        <v>141.19999999999999</v>
       </c>
       <c r="G188" s="1">
         <v>21.1</v>
@@ -8665,7 +8975,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>429</v>
       </c>
@@ -8682,7 +8992,7 @@
         <v>166180</v>
       </c>
       <c r="F189" s="1">
-        <v>4247.1</v>
+        <v>4247.1000000000004</v>
       </c>
       <c r="G189" s="1">
         <v>47.5</v>
@@ -8691,7 +9001,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>431</v>
       </c>
@@ -8708,7 +9018,7 @@
         <v>2834.4</v>
       </c>
       <c r="F190" s="1">
-        <v>72.4</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="G190" s="1">
         <v>27.1</v>
@@ -8717,7 +9027,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>433</v>
       </c>
@@ -8737,13 +9047,13 @@
         <v>13.8</v>
       </c>
       <c r="G191" s="1">
-        <v>65.9</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="H191" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>435</v>
       </c>
@@ -8754,7 +9064,7 @@
         <v>221</v>
       </c>
       <c r="D192" s="1">
-        <v>71.6</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="E192" s="1">
         <v>35800</v>
@@ -8763,13 +9073,13 @@
         <v>914.9</v>
       </c>
       <c r="G192" s="1">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H192" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>437</v>
       </c>
@@ -8780,7 +9090,7 @@
         <v>126</v>
       </c>
       <c r="D193" s="1">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="E193" s="1">
         <v>1755.1</v>
@@ -8795,7 +9105,7 @@
         <v>704.8</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>439</v>
       </c>
@@ -8821,7 +9131,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>441</v>
       </c>
@@ -8832,10 +9142,10 @@
         <v>99</v>
       </c>
       <c r="D195" s="1">
-        <v>9.88</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="E195" s="1">
-        <v>1185.6</v>
+        <v>1185.5999999999999</v>
       </c>
       <c r="F195" s="1">
         <v>30.3</v>
@@ -8847,7 +9157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>443</v>
       </c>
@@ -8873,7 +9183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>445</v>
       </c>
@@ -8899,7 +9209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>447</v>
       </c>
@@ -8913,7 +9223,7 @@
         <v>14.48</v>
       </c>
       <c r="E198" s="1">
-        <v>289.6</v>
+        <v>289.60000000000002</v>
       </c>
       <c r="F198" s="1">
         <v>7.4</v>
@@ -8925,7 +9235,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>449</v>
       </c>
@@ -8951,7 +9261,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>451</v>
       </c>
@@ -8977,7 +9287,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>453</v>
       </c>
@@ -9003,7 +9313,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>455</v>
       </c>
@@ -9029,7 +9339,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>457</v>
       </c>
@@ -9055,7 +9365,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>459</v>
       </c>
@@ -9081,7 +9391,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>461</v>
       </c>
@@ -9098,7 +9408,7 @@
         <v>11655</v>
       </c>
       <c r="F205" s="1">
-        <v>297.9</v>
+        <v>297.89999999999998</v>
       </c>
       <c r="G205" s="1">
         <v>37.6</v>
@@ -9107,7 +9417,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>463</v>
       </c>
@@ -9133,7 +9443,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>465</v>
       </c>
@@ -9159,7 +9469,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>467</v>
       </c>
@@ -9185,7 +9495,7 @@
         <v>3509.1</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>469</v>
       </c>
@@ -9199,7 +9509,7 @@
         <v>3.9</v>
       </c>
       <c r="E209" s="1">
-        <v>4197.4</v>
+        <v>4197.3999999999996</v>
       </c>
       <c r="F209" s="1">
         <v>107.3</v>
@@ -9211,7 +9521,7 @@
         <v>1076.3</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>471</v>
       </c>
@@ -9231,13 +9541,13 @@
         <v>119.9</v>
       </c>
       <c r="G210" s="1">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H210" s="1">
         <v>67</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>473</v>
       </c>
@@ -9263,7 +9573,7 @@
         <v>147.1</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>475</v>
       </c>
@@ -9289,7 +9599,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>477</v>
       </c>
@@ -9315,7 +9625,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>479</v>
       </c>
@@ -9341,7 +9651,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>481</v>
       </c>
@@ -9367,7 +9677,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>483</v>
       </c>
@@ -9393,7 +9703,7 @@
         <v>397.5</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>485</v>
       </c>
@@ -9419,7 +9729,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>487</v>
       </c>
@@ -9445,7 +9755,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>489</v>
       </c>
@@ -9471,7 +9781,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>491</v>
       </c>
@@ -9485,19 +9795,19 @@
         <v>59.35</v>
       </c>
       <c r="E220" s="1">
-        <v>8291.2</v>
+        <v>8291.2000000000007</v>
       </c>
       <c r="F220" s="1">
         <v>211.9</v>
       </c>
       <c r="G220" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H220" s="1">
-        <v>139.7</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>139.69999999999999</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>493</v>
       </c>
@@ -9514,7 +9824,7 @@
         <v>43200</v>
       </c>
       <c r="F221" s="1">
-        <v>1104.1</v>
+        <v>1104.0999999999999</v>
       </c>
       <c r="G221" s="1">
         <v>24</v>
@@ -9523,7 +9833,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>495</v>
       </c>
@@ -9549,7 +9859,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>497</v>
       </c>
@@ -9569,13 +9879,13 @@
         <v>68.8</v>
       </c>
       <c r="G223" s="1">
-        <v>80.9</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="H223" s="1">
         <v>240</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>499</v>
       </c>
@@ -9601,7 +9911,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>501</v>
       </c>
@@ -9615,7 +9925,7 @@
         <v>16.62</v>
       </c>
       <c r="E225" s="1">
-        <v>2479.7</v>
+        <v>2479.6999999999998</v>
       </c>
       <c r="F225" s="1">
         <v>63.4</v>
@@ -9624,10 +9934,10 @@
         <v>99.5</v>
       </c>
       <c r="H225" s="1">
-        <v>149.2</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>149.19999999999999</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>503</v>
       </c>
@@ -9653,7 +9963,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>505</v>
       </c>
@@ -9667,7 +9977,7 @@
         <v>10.3</v>
       </c>
       <c r="E227" s="1">
-        <v>1215.4</v>
+        <v>1215.4000000000001</v>
       </c>
       <c r="F227" s="1">
         <v>31.1</v>
@@ -9679,7 +9989,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>507</v>
       </c>
@@ -9699,13 +10009,13 @@
         <v>374.8</v>
       </c>
       <c r="G228" s="1">
-        <v>65.9</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="H228" s="1">
         <v>1950</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>509</v>
       </c>
@@ -9731,7 +10041,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>511</v>
       </c>
@@ -9757,7 +10067,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>513</v>
       </c>
@@ -9774,7 +10084,7 @@
         <v>1261.5</v>
       </c>
       <c r="F231" s="1">
-        <v>32.2</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="G231" s="1">
         <v>32</v>
@@ -9783,7 +10093,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>515</v>
       </c>
@@ -9809,7 +10119,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>517</v>
       </c>
@@ -9835,7 +10145,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>519</v>
       </c>
@@ -9861,7 +10171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>521</v>
       </c>
@@ -9887,7 +10197,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>523</v>
       </c>
@@ -9901,7 +10211,7 @@
         <v>242.9</v>
       </c>
       <c r="E236" s="1">
-        <v>81128.6</v>
+        <v>81128.600000000006</v>
       </c>
       <c r="F236" s="1">
         <v>2073.4</v>
@@ -9913,7 +10223,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>525</v>
       </c>
@@ -9933,13 +10243,13 @@
         <v>49.4</v>
       </c>
       <c r="G237" s="1">
-        <v>79.4</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="H237" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>527</v>
       </c>
@@ -9956,16 +10266,16 @@
         <v>43583.3</v>
       </c>
       <c r="F238" s="1">
-        <v>1113.9</v>
+        <v>1113.9000000000001</v>
       </c>
       <c r="G238" s="1">
         <v>12</v>
       </c>
       <c r="H238" s="1">
-        <v>322.6</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>322.60000000000002</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>529</v>
       </c>
@@ -9991,7 +10301,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>531</v>
       </c>
@@ -10017,7 +10327,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>533</v>
       </c>
@@ -10037,13 +10347,13 @@
         <v>323</v>
       </c>
       <c r="G241" s="1">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H241" s="1">
         <v>132</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>535</v>
       </c>
@@ -10057,7 +10367,7 @@
         <v>2.69</v>
       </c>
       <c r="E242" s="1">
-        <v>9899.2</v>
+        <v>9899.2000000000007</v>
       </c>
       <c r="F242" s="1">
         <v>253</v>
@@ -10069,7 +10379,7 @@
         <v>3680</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>537</v>
       </c>
@@ -10080,7 +10390,7 @@
         <v>44</v>
       </c>
       <c r="D243" s="1">
-        <v>20.44</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="E243" s="1">
         <v>146856.9</v>
@@ -10095,7 +10405,7 @@
         <v>7184.8</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>539</v>
       </c>
@@ -10109,7 +10419,7 @@
         <v>81.5</v>
       </c>
       <c r="E244" s="1">
-        <v>9388.8</v>
+        <v>9388.7999999999993</v>
       </c>
       <c r="F244" s="1">
         <v>240</v>
@@ -10121,7 +10431,7 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>541</v>
       </c>
@@ -10132,10 +10442,10 @@
         <v>221</v>
       </c>
       <c r="D245" s="1">
-        <v>38.66</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="E245" s="1">
-        <v>8563.2</v>
+        <v>8563.2000000000007</v>
       </c>
       <c r="F245" s="1">
         <v>218.9</v>
@@ -10147,7 +10457,7 @@
         <v>221.5</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>543</v>
       </c>
@@ -10164,16 +10474,16 @@
         <v>1575</v>
       </c>
       <c r="F246" s="1">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="G246" s="1">
-        <v>67.6</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="H246" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>545</v>
       </c>
@@ -10190,7 +10500,7 @@
         <v>1480.3</v>
       </c>
       <c r="F247" s="1">
-        <v>37.8</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="G247" s="1">
         <v>78.7</v>
@@ -10199,7 +10509,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>547</v>
       </c>
@@ -10210,7 +10520,7 @@
         <v>13</v>
       </c>
       <c r="D248" s="1">
-        <v>9.03</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="E248" s="1">
         <v>16931.3</v>
@@ -10225,7 +10535,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>549</v>
       </c>
@@ -10251,7 +10561,7 @@
         <v>8430</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>551</v>
       </c>
@@ -10265,7 +10575,7 @@
         <v>10.62</v>
       </c>
       <c r="E250" s="1">
-        <v>1115.1</v>
+        <v>1115.0999999999999</v>
       </c>
       <c r="F250" s="1">
         <v>28.5</v>
@@ -10277,7 +10587,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>553</v>
       </c>
@@ -10303,7 +10613,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>555</v>
       </c>
@@ -10317,7 +10627,7 @@
         <v>47.3</v>
       </c>
       <c r="E252" s="1">
-        <v>4280.1</v>
+        <v>4280.1000000000004</v>
       </c>
       <c r="F252" s="1">
         <v>109.4</v>
@@ -10329,7 +10639,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>557</v>
       </c>
@@ -10355,7 +10665,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>559</v>
       </c>
@@ -10381,7 +10691,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>561</v>
       </c>
@@ -10407,7 +10717,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>563</v>
       </c>
@@ -10433,7 +10743,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>565</v>
       </c>
@@ -10459,7 +10769,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>567</v>
       </c>
@@ -10485,7 +10795,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>569</v>
       </c>
@@ -10502,7 +10812,7 @@
         <v>3048</v>
       </c>
       <c r="F259" s="1">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="G259" s="1">
         <v>25.1</v>
@@ -10511,7 +10821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>571</v>
       </c>
@@ -10537,7 +10847,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>573</v>
       </c>
@@ -10563,7 +10873,7 @@
         <v>543.6</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>575</v>
       </c>
@@ -10589,7 +10899,7 @@
         <v>212.9</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>577</v>
       </c>
@@ -10615,7 +10925,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>579</v>
       </c>
@@ -10632,7 +10942,7 @@
         <v>701</v>
       </c>
       <c r="F264" s="1">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="G264" s="1">
         <v>74.3</v>
@@ -10641,7 +10951,7 @@
         <v>350.5</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>581</v>
       </c>
@@ -10667,7 +10977,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>583</v>
       </c>
@@ -10693,7 +11003,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>585</v>
       </c>
@@ -10719,7 +11029,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>587</v>
       </c>
@@ -10745,7 +11055,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>589</v>
       </c>
@@ -10765,13 +11075,13 @@
         <v>24.6</v>
       </c>
       <c r="G269" s="1">
-        <v>73.9</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="H269" s="1">
         <v>450</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>591</v>
       </c>
@@ -10788,7 +11098,7 @@
         <v>2756.5</v>
       </c>
       <c r="F270" s="1">
-        <v>70.4</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="G270" s="1">
         <v>67.3</v>
@@ -10797,7 +11107,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>593</v>
       </c>
@@ -10823,7 +11133,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>595</v>
       </c>
@@ -10834,7 +11144,7 @@
         <v>16</v>
       </c>
       <c r="D272" s="1">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E272" s="1">
         <v>2189.6</v>
@@ -10849,7 +11159,7 @@
         <v>960.3</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>597</v>
       </c>
@@ -10875,7 +11185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>599</v>
       </c>
@@ -10898,10 +11208,10 @@
         <v>12.6</v>
       </c>
       <c r="H274" s="1">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="275">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>601</v>
       </c>
@@ -10921,13 +11231,13 @@
         <v>162</v>
       </c>
       <c r="G275" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H275" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>603</v>
       </c>
@@ -10953,7 +11263,7 @@
         <v>259.8</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>605</v>
       </c>
@@ -10979,7 +11289,7 @@
         <v>160.6</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>607</v>
       </c>
@@ -10999,13 +11309,13 @@
         <v>2610.4</v>
       </c>
       <c r="G278" s="1">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H278" s="1">
         <v>2900</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>609</v>
       </c>
@@ -11031,7 +11341,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>611</v>
       </c>
@@ -11054,10 +11364,10 @@
         <v>24</v>
       </c>
       <c r="H280" s="1">
-        <v>2443.8</v>
-      </c>
-    </row>
-    <row r="281">
+        <v>2443.8000000000002</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>613</v>
       </c>
@@ -11068,7 +11378,7 @@
         <v>262</v>
       </c>
       <c r="D281" s="1">
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="E281" s="1">
         <v>7530</v>
@@ -11083,7 +11393,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>615</v>
       </c>
@@ -11109,7 +11419,7 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>617</v>
       </c>
@@ -11135,7 +11445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>619</v>
       </c>
@@ -11161,7 +11471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>621</v>
       </c>
@@ -11187,7 +11497,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>623</v>
       </c>
@@ -11213,7 +11523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>625</v>
       </c>
@@ -11239,7 +11549,7 @@
         <v>695.3</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>627</v>
       </c>
@@ -11253,10 +11563,10 @@
         <v>35.04</v>
       </c>
       <c r="E288" s="1">
-        <v>2615.8</v>
+        <v>2615.8000000000002</v>
       </c>
       <c r="F288" s="1">
-        <v>66.9</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="G288" s="1">
         <v>40.1</v>
@@ -11265,7 +11575,7 @@
         <v>74.7</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>629</v>
       </c>
@@ -11285,13 +11595,13 @@
         <v>372.4</v>
       </c>
       <c r="G289" s="1">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H289" s="1">
         <v>958.8</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>631</v>
       </c>
@@ -11317,7 +11627,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>633</v>
       </c>
@@ -11334,7 +11644,7 @@
         <v>2558.6</v>
       </c>
       <c r="F291" s="1">
-        <v>65.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="G291" s="1">
         <v>41</v>
@@ -11343,7 +11653,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>635</v>
       </c>
@@ -11369,7 +11679,7 @@
         <v>424.4</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>637</v>
       </c>
@@ -11395,7 +11705,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>639</v>
       </c>
@@ -11421,7 +11731,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>641</v>
       </c>
@@ -11447,7 +11757,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>643</v>
       </c>
@@ -11470,10 +11780,10 @@
         <v>21.2</v>
       </c>
       <c r="H296" s="1">
-        <v>514.8</v>
-      </c>
-    </row>
-    <row r="297">
+        <v>514.79999999999995</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>645</v>
       </c>
@@ -11499,7 +11809,7 @@
         <v>411.4</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>647</v>
       </c>
@@ -11525,7 +11835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>649</v>
       </c>
@@ -11539,10 +11849,10 @@
         <v>42</v>
       </c>
       <c r="E299" s="1">
-        <v>10092.8</v>
+        <v>10092.799999999999</v>
       </c>
       <c r="F299" s="1">
-        <v>257.9</v>
+        <v>257.89999999999998</v>
       </c>
       <c r="G299" s="1">
         <v>98.5</v>
@@ -11551,7 +11861,7 @@
         <v>240.3</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>651</v>
       </c>
@@ -11568,7 +11878,7 @@
         <v>2716.8</v>
       </c>
       <c r="F300" s="1">
-        <v>69.4</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="G300" s="1">
         <v>97.8</v>
@@ -11577,7 +11887,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>653</v>
       </c>
@@ -11591,7 +11901,7 @@
         <v>23.7</v>
       </c>
       <c r="E301" s="1">
-        <v>18491.4</v>
+        <v>18491.400000000001</v>
       </c>
       <c r="F301" s="1">
         <v>472.6</v>
@@ -11603,7 +11913,7 @@
         <v>780.2</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>655</v>
       </c>
@@ -11629,7 +11939,7 @@
         <v>805.9</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>657</v>
       </c>
@@ -11655,7 +11965,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>659</v>
       </c>
@@ -11681,7 +11991,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>661</v>
       </c>
@@ -11707,7 +12017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>663</v>
       </c>
@@ -11724,7 +12034,7 @@
         <v>6075</v>
       </c>
       <c r="F306" s="1">
-        <v>155.3</v>
+        <v>155.30000000000001</v>
       </c>
       <c r="G306" s="1">
         <v>21.8</v>
@@ -11733,7 +12043,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>665</v>
       </c>
@@ -11756,10 +12066,10 @@
         <v>79.8</v>
       </c>
       <c r="H307" s="1">
-        <v>2153.3</v>
-      </c>
-    </row>
-    <row r="308">
+        <v>2153.3000000000002</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>667</v>
       </c>
@@ -11785,7 +12095,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>669</v>
       </c>
@@ -11811,7 +12121,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>671</v>
       </c>
@@ -11828,7 +12138,7 @@
         <v>165000</v>
       </c>
       <c r="F310" s="1">
-        <v>4216.9</v>
+        <v>4216.8999999999996</v>
       </c>
       <c r="G310" s="1">
         <v>0.5</v>
@@ -11837,7 +12147,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>673</v>
       </c>
@@ -11863,7 +12173,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>675</v>
       </c>
@@ -11889,7 +12199,7 @@
         <v>588.5</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>677</v>
       </c>
@@ -11915,7 +12225,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>679</v>
       </c>
@@ -11926,7 +12236,7 @@
         <v>13</v>
       </c>
       <c r="D314" s="1">
-        <v>67.1</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="E314" s="1">
         <v>109037.5</v>
@@ -11941,7 +12251,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>681</v>
       </c>
@@ -11967,7 +12277,7 @@
         <v>486.2</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>683</v>
       </c>
@@ -11993,7 +12303,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>685</v>
       </c>
@@ -12019,7 +12329,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>687</v>
       </c>
@@ -12045,7 +12355,7 @@
         <v>431.4</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>689</v>
       </c>
@@ -12071,7 +12381,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>691</v>
       </c>
@@ -12097,7 +12407,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>693</v>
       </c>
@@ -12123,7 +12433,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>695</v>
       </c>
@@ -12146,10 +12456,10 @@
         <v>16</v>
       </c>
       <c r="H322" s="1">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="323">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>697</v>
       </c>
@@ -12175,7 +12485,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>699</v>
       </c>
@@ -12192,7 +12502,7 @@
         <v>11049.3</v>
       </c>
       <c r="F324" s="1">
-        <v>282.4</v>
+        <v>282.39999999999998</v>
       </c>
       <c r="G324" s="1">
         <v>28.6</v>
@@ -12201,7 +12511,7 @@
         <v>194.5</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>701</v>
       </c>
@@ -12218,7 +12528,7 @@
         <v>2811.6</v>
       </c>
       <c r="F325" s="1">
-        <v>71.9</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="G325" s="1">
         <v>25.4</v>
@@ -12227,7 +12537,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>703</v>
       </c>
@@ -12253,7 +12563,7 @@
         <v>174.6</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>705</v>
       </c>
@@ -12279,7 +12589,7 @@
         <v>829.7</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>707</v>
       </c>
@@ -12305,7 +12615,7 @@
         <v>3202.5</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>709</v>
       </c>
@@ -12319,7 +12629,7 @@
         <v>88.05</v>
       </c>
       <c r="E329" s="1">
-        <v>34170.4</v>
+        <v>34170.400000000001</v>
       </c>
       <c r="F329" s="1">
         <v>873.3</v>
@@ -12331,7 +12641,7 @@
         <v>388.1</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>711</v>
       </c>
@@ -12357,7 +12667,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>713</v>
       </c>
@@ -12374,7 +12684,7 @@
         <v>378102.4</v>
       </c>
       <c r="F331" s="1">
-        <v>9663.2</v>
+        <v>9663.2000000000007</v>
       </c>
       <c r="G331" s="1">
         <v>26.4</v>
@@ -12383,7 +12693,7 @@
         <v>2535.9</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>715</v>
       </c>
@@ -12400,7 +12710,7 @@
         <v>5660.2</v>
       </c>
       <c r="F332" s="1">
-        <v>144.7</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="G332" s="1">
         <v>23.6</v>
@@ -12409,7 +12719,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>717</v>
       </c>
@@ -12435,7 +12745,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>719</v>
       </c>
@@ -12452,16 +12762,16 @@
         <v>1438.3</v>
       </c>
       <c r="F334" s="1">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="G334" s="1">
-        <v>65.1</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="H334" s="1">
         <v>85.6</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>722</v>
       </c>
@@ -12481,13 +12791,13 @@
         <v>72</v>
       </c>
       <c r="G335" s="1">
-        <v>72.4</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H335" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>724</v>
       </c>
@@ -12513,7 +12823,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>726</v>
       </c>
@@ -12539,7 +12849,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>728</v>
       </c>
@@ -12565,7 +12875,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>730</v>
       </c>
@@ -12591,7 +12901,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>732</v>
       </c>
@@ -12617,7 +12927,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>734</v>
       </c>
@@ -12643,7 +12953,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>736</v>
       </c>
@@ -12669,7 +12979,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>738</v>
       </c>
@@ -12689,13 +12999,13 @@
         <v>320.8</v>
       </c>
       <c r="G343" s="1">
-        <v>34.8</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="H343" s="1">
         <v>1200</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>740</v>
       </c>
@@ -12721,7 +13031,7 @@
         <v>558.4</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>742</v>
       </c>
@@ -12747,7 +13057,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>744</v>
       </c>
@@ -12773,7 +13083,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>746</v>
       </c>
@@ -12796,10 +13106,10 @@
         <v>30.2</v>
       </c>
       <c r="H347" s="1">
-        <v>516.2</v>
-      </c>
-    </row>
-    <row r="348">
+        <v>516.20000000000005</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>748</v>
       </c>
@@ -12825,7 +13135,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>750</v>
       </c>
@@ -12836,7 +13146,7 @@
         <v>126</v>
       </c>
       <c r="D349" s="1">
-        <v>144.8</v>
+        <v>144.80000000000001</v>
       </c>
       <c r="E349" s="1">
         <v>13756</v>
@@ -12851,7 +13161,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>752</v>
       </c>
@@ -12877,7 +13187,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>754</v>
       </c>
@@ -12897,13 +13207,13 @@
         <v>102.5</v>
       </c>
       <c r="G351" s="1">
-        <v>79.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="H351" s="1">
         <v>768</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>756</v>
       </c>
@@ -12917,7 +13227,7 @@
         <v>93.05</v>
       </c>
       <c r="E352" s="1">
-        <v>19354.4</v>
+        <v>19354.400000000001</v>
       </c>
       <c r="F352" s="1">
         <v>494.6</v>
@@ -12929,7 +13239,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>758</v>
       </c>
@@ -12955,7 +13265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>760</v>
       </c>
@@ -12981,7 +13291,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>762</v>
       </c>
@@ -13007,7 +13317,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>764</v>
       </c>
@@ -13033,7 +13343,7 @@
         <v>165.5</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>766</v>
       </c>
@@ -13059,7 +13369,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>768</v>
       </c>
@@ -13085,7 +13395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>770</v>
       </c>
@@ -13111,7 +13421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>772</v>
       </c>
@@ -13137,7 +13447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>774</v>
       </c>
@@ -13163,7 +13473,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>776</v>
       </c>
@@ -13189,7 +13499,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>778</v>
       </c>
@@ -13215,7 +13525,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>780</v>
       </c>
@@ -13232,16 +13542,16 @@
         <v>25106.6</v>
       </c>
       <c r="F364" s="1">
-        <v>641.7</v>
+        <v>641.70000000000005</v>
       </c>
       <c r="G364" s="1">
-        <v>72.6</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="H364" s="1">
         <v>794.5</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>782</v>
       </c>
@@ -13255,19 +13565,19 @@
         <v>5.88</v>
       </c>
       <c r="E365" s="1">
-        <v>638.3</v>
+        <v>638.29999999999995</v>
       </c>
       <c r="F365" s="1">
         <v>16.3</v>
       </c>
       <c r="G365" s="1">
-        <v>66.4</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="H365" s="1">
         <v>108.6</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>784</v>
       </c>
@@ -13293,7 +13603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>787</v>
       </c>
@@ -13319,7 +13629,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>789</v>
       </c>
@@ -13345,7 +13655,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>791</v>
       </c>
@@ -13365,13 +13675,13 @@
         <v>19.8</v>
       </c>
       <c r="G369" s="1">
-        <v>76.1</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="H369" s="1">
         <v>275</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>793</v>
       </c>
@@ -13382,7 +13692,7 @@
         <v>123</v>
       </c>
       <c r="D370" s="1">
-        <v>39.88</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="E370" s="1">
         <v>2492.5</v>
@@ -13397,7 +13707,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>795</v>
       </c>
@@ -13414,7 +13724,7 @@
         <v>2958.7</v>
       </c>
       <c r="F371" s="1">
-        <v>75.6</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="G371" s="1">
         <v>49.6</v>
@@ -13423,7 +13733,7 @@
         <v>277.3</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>797</v>
       </c>
@@ -13440,7 +13750,7 @@
         <v>2912.7</v>
       </c>
       <c r="F372" s="1">
-        <v>74.4</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="G372" s="1">
         <v>28.8</v>
@@ -13449,7 +13759,7 @@
         <v>190.4</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>799</v>
       </c>
@@ -13475,7 +13785,7 @@
         <v>336.6</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>801</v>
       </c>
@@ -13495,13 +13805,13 @@
         <v>35.1</v>
       </c>
       <c r="G374" s="1">
-        <v>78.4</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="H374" s="1">
         <v>101.1</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>803</v>
       </c>
@@ -13527,7 +13837,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>805</v>
       </c>
@@ -13550,10 +13860,10 @@
         <v>52.6</v>
       </c>
       <c r="H376" s="1">
-        <v>75.4</v>
-      </c>
-    </row>
-    <row r="377">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>807</v>
       </c>
@@ -13570,7 +13880,7 @@
         <v>1414.8</v>
       </c>
       <c r="F377" s="1">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="G377" s="1">
         <v>60.1</v>
@@ -13579,7 +13889,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>809</v>
       </c>
@@ -13593,7 +13903,7 @@
         <v>6.49</v>
       </c>
       <c r="E378" s="1">
-        <v>272.6</v>
+        <v>272.60000000000002</v>
       </c>
       <c r="F378" s="1">
         <v>7</v>
@@ -13605,7 +13915,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>811</v>
       </c>
@@ -13631,7 +13941,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>813</v>
       </c>
@@ -13657,7 +13967,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>815</v>
       </c>
@@ -13683,7 +13993,7 @@
         <v>181.1</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>817</v>
       </c>
@@ -13709,7 +14019,7 @@
         <v>469.8</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>819</v>
       </c>
@@ -13723,7 +14033,7 @@
         <v>334.5</v>
       </c>
       <c r="E383" s="1">
-        <v>63893.6</v>
+        <v>63893.599999999999</v>
       </c>
       <c r="F383" s="1">
         <v>1632.9</v>
@@ -13735,7 +14045,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>821</v>
       </c>
@@ -13749,10 +14059,10 @@
         <v>24.3</v>
       </c>
       <c r="E384" s="1">
-        <v>324.1</v>
+        <v>324.10000000000002</v>
       </c>
       <c r="F384" s="1">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G384" s="1">
         <v>92.1</v>
@@ -13761,7 +14071,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>823</v>
       </c>
@@ -13787,7 +14097,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>825</v>
       </c>
@@ -13813,7 +14123,7 @@
         <v>2440.1</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>827</v>
       </c>
@@ -13830,7 +14140,7 @@
         <v>5685.8</v>
       </c>
       <c r="F387" s="1">
-        <v>145.3</v>
+        <v>145.30000000000001</v>
       </c>
       <c r="G387" s="1">
         <v>15.3</v>
@@ -13839,7 +14149,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>829</v>
       </c>
@@ -13850,7 +14160,7 @@
         <v>234</v>
       </c>
       <c r="D388" s="1">
-        <v>32.48</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="E388" s="1">
         <v>8867</v>
@@ -13865,7 +14175,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>831</v>
       </c>
@@ -13891,7 +14201,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>833</v>
       </c>
@@ -13917,7 +14227,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>835</v>
       </c>
@@ -13934,7 +14244,7 @@
         <v>20750</v>
       </c>
       <c r="F391" s="1">
-        <v>530.3</v>
+        <v>530.29999999999995</v>
       </c>
       <c r="G391" s="1">
         <v>22.6</v>
@@ -13943,7 +14253,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>837</v>
       </c>
@@ -13960,16 +14270,16 @@
         <v>3183.6</v>
       </c>
       <c r="F392" s="1">
-        <v>81.4</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="G392" s="1">
         <v>36.9</v>
       </c>
       <c r="H392" s="1">
-        <v>64.9</v>
-      </c>
-    </row>
-    <row r="393">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>839</v>
       </c>
@@ -13989,13 +14299,13 @@
         <v>23.5</v>
       </c>
       <c r="G393" s="1">
-        <v>76.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="H393" s="1">
         <v>54</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>841</v>
       </c>
@@ -14015,13 +14325,13 @@
         <v>855.7</v>
       </c>
       <c r="G394" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H394" s="1">
-        <v>150.2</v>
-      </c>
-    </row>
-    <row r="395">
+        <v>150.19999999999999</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>843</v>
       </c>
@@ -14047,7 +14357,7 @@
         <v>335.3</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>845</v>
       </c>
@@ -14073,7 +14383,7 @@
         <v>479.4</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>847</v>
       </c>
@@ -14099,7 +14409,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>849</v>
       </c>
@@ -14119,13 +14429,13 @@
         <v>178.9</v>
       </c>
       <c r="G398" s="1">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="H398" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>851</v>
       </c>
@@ -14136,10 +14446,10 @@
         <v>126</v>
       </c>
       <c r="D399" s="1">
-        <v>76.4</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="E399" s="1">
-        <v>8442.2</v>
+        <v>8442.2000000000007</v>
       </c>
       <c r="F399" s="1">
         <v>215.8</v>
@@ -14151,7 +14461,7 @@
         <v>110.5</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>853</v>
       </c>
@@ -14174,10 +14484,10 @@
         <v>15.5</v>
       </c>
       <c r="H400" s="1">
-        <v>146.3</v>
-      </c>
-    </row>
-    <row r="401">
+        <v>146.30000000000001</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>855</v>
       </c>
@@ -14197,13 +14507,13 @@
         <v>51.6</v>
       </c>
       <c r="G401" s="1">
-        <v>36.3</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="H401" s="1">
         <v>23.9</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>857</v>
       </c>
@@ -14229,7 +14539,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>859</v>
       </c>
@@ -14240,13 +14550,13 @@
         <v>10</v>
       </c>
       <c r="D403" s="1">
-        <v>77.6</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="E403" s="1">
         <v>6208</v>
       </c>
       <c r="F403" s="1">
-        <v>158.7</v>
+        <v>158.69999999999999</v>
       </c>
       <c r="G403" s="1">
         <v>52.3</v>
@@ -14255,7 +14565,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>861</v>
       </c>
@@ -14269,7 +14579,7 @@
         <v>162</v>
       </c>
       <c r="E404" s="1">
-        <v>4406.4</v>
+        <v>4406.3999999999996</v>
       </c>
       <c r="F404" s="1">
         <v>112.6</v>
@@ -14281,7 +14591,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>863</v>
       </c>
@@ -14307,7 +14617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>865</v>
       </c>
@@ -14333,7 +14643,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>867</v>
       </c>
@@ -14347,7 +14657,7 @@
         <v>4.33</v>
       </c>
       <c r="E407" s="1">
-        <v>2554.7</v>
+        <v>2554.6999999999998</v>
       </c>
       <c r="F407" s="1">
         <v>65.3</v>
@@ -14359,7 +14669,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>869</v>
       </c>
@@ -14385,7 +14695,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>871</v>
       </c>
@@ -14411,7 +14721,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>873</v>
       </c>
@@ -14437,7 +14747,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>875</v>
       </c>
@@ -14463,7 +14773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>877</v>
       </c>
@@ -14483,13 +14793,13 @@
         <v>2693.7</v>
       </c>
       <c r="G412" s="1">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H412" s="1">
         <v>4861.7</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>879</v>
       </c>
@@ -14503,19 +14813,19 @@
         <v>7.18</v>
       </c>
       <c r="E413" s="1">
-        <v>610.3</v>
+        <v>610.29999999999995</v>
       </c>
       <c r="F413" s="1">
         <v>15.6</v>
       </c>
       <c r="G413" s="1">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="H413" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>881</v>
       </c>
@@ -14541,7 +14851,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>883</v>
       </c>
@@ -14567,7 +14877,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>885</v>
       </c>
@@ -14578,7 +14888,7 @@
         <v>25</v>
       </c>
       <c r="D416" s="1">
-        <v>70.4</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="E416" s="1">
         <v>6124.8</v>
@@ -14593,7 +14903,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>887</v>
       </c>
@@ -14619,7 +14929,7 @@
         <v>206.3</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>889</v>
       </c>
@@ -14645,7 +14955,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>891</v>
       </c>
@@ -14656,7 +14966,7 @@
         <v>304</v>
       </c>
       <c r="D419" s="1">
-        <v>17.17</v>
+        <v>17.170000000000002</v>
       </c>
       <c r="E419" s="1">
         <v>2556.1</v>
@@ -14671,7 +14981,7 @@
         <v>148.9</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>893</v>
       </c>
@@ -14682,7 +14992,7 @@
         <v>186</v>
       </c>
       <c r="D420" s="1">
-        <v>77.1</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="E420" s="1">
         <v>5945.3</v>
@@ -14694,10 +15004,10 @@
         <v>29.8</v>
       </c>
       <c r="H420" s="1">
-        <v>77.1</v>
-      </c>
-    </row>
-    <row r="421">
+        <v>77.099999999999994</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>895</v>
       </c>
@@ -14708,10 +15018,10 @@
         <v>221</v>
       </c>
       <c r="D421" s="1">
-        <v>76.65</v>
+        <v>76.650000000000006</v>
       </c>
       <c r="E421" s="1">
-        <v>51508.8</v>
+        <v>51508.800000000003</v>
       </c>
       <c r="F421" s="1">
         <v>1316.4</v>
@@ -14723,7 +15033,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>897</v>
       </c>
@@ -14749,7 +15059,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>899</v>
       </c>
@@ -14775,7 +15085,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>901</v>
       </c>
@@ -14795,13 +15105,13 @@
         <v>40</v>
       </c>
       <c r="G424" s="1">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="H424" s="1">
         <v>118.4</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>903</v>
       </c>
@@ -14827,7 +15137,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>906</v>
       </c>
@@ -14853,7 +15163,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>908</v>
       </c>
@@ -14879,7 +15189,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>910</v>
       </c>
@@ -14899,13 +15209,13 @@
         <v>131.4</v>
       </c>
       <c r="G428" s="1">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H428" s="1">
         <v>393.5</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>912</v>
       </c>
@@ -14916,7 +15226,7 @@
         <v>13</v>
       </c>
       <c r="D429" s="1">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="E429" s="1">
         <v>16026.6</v>
@@ -14931,7 +15241,7 @@
         <v>997.9</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>914</v>
       </c>
@@ -14957,7 +15267,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>916</v>
       </c>
@@ -14983,7 +15293,7 @@
         <v>2534.4</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>918</v>
       </c>
@@ -15003,13 +15313,13 @@
         <v>139.9</v>
       </c>
       <c r="G432" s="1">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H432" s="1">
         <v>24.9</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>920</v>
       </c>
@@ -15026,16 +15336,16 @@
         <v>1517.4</v>
       </c>
       <c r="F433" s="1">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="G433" s="1">
-        <v>33.8</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H433" s="1">
         <v>22.8</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>922</v>
       </c>
@@ -15052,7 +15362,7 @@
         <v>6094.3</v>
       </c>
       <c r="F434" s="1">
-        <v>155.8</v>
+        <v>155.80000000000001</v>
       </c>
       <c r="G434" s="1">
         <v>20.2</v>
@@ -15061,7 +15371,7 @@
         <v>244.8</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>924</v>
       </c>
@@ -15087,7 +15397,7 @@
         <v>758.5</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>926</v>
       </c>
@@ -15104,7 +15414,7 @@
         <v>23071.9</v>
       </c>
       <c r="F436" s="1">
-        <v>589.7</v>
+        <v>589.70000000000005</v>
       </c>
       <c r="G436" s="1">
         <v>22.7</v>
@@ -15113,7 +15423,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>928</v>
       </c>
@@ -15139,7 +15449,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>930</v>
       </c>
@@ -15156,7 +15466,7 @@
         <v>5765.1</v>
       </c>
       <c r="F438" s="1">
-        <v>147.3</v>
+        <v>147.30000000000001</v>
       </c>
       <c r="G438" s="1">
         <v>16.2</v>
@@ -15165,7 +15475,7 @@
         <v>216.7</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>932</v>
       </c>
@@ -15176,13 +15486,13 @@
         <v>99</v>
       </c>
       <c r="D439" s="1">
-        <v>8.78</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="E439" s="1">
         <v>2663.4</v>
       </c>
       <c r="F439" s="1">
-        <v>68.1</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="G439" s="1">
         <v>33.1</v>
@@ -15191,7 +15501,7 @@
         <v>303.3</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>934</v>
       </c>
@@ -15211,13 +15521,13 @@
         <v>42.7</v>
       </c>
       <c r="G440" s="1">
-        <v>32.3</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="H440" s="1">
         <v>284.3</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>936</v>
       </c>
@@ -15243,7 +15553,7 @@
         <v>314.7</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>938</v>
       </c>
@@ -15269,7 +15579,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>940</v>
       </c>
@@ -15295,7 +15605,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>942</v>
       </c>
@@ -15321,7 +15631,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>944</v>
       </c>
@@ -15347,7 +15657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>946</v>
       </c>
@@ -15367,13 +15677,13 @@
         <v>838.3</v>
       </c>
       <c r="G446" s="1">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="H446" s="1">
         <v>333</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>948</v>
       </c>
@@ -15399,7 +15709,7 @@
         <v>163.1</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>950</v>
       </c>
@@ -15425,7 +15735,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>952</v>
       </c>
@@ -15451,7 +15761,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>954</v>
       </c>
@@ -15477,7 +15787,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>956</v>
       </c>
@@ -15488,7 +15798,7 @@
         <v>74</v>
       </c>
       <c r="D451" s="1">
-        <v>16.26</v>
+        <v>16.260000000000002</v>
       </c>
       <c r="E451" s="1">
         <v>460.8</v>
@@ -15503,7 +15813,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>958</v>
       </c>
@@ -15529,7 +15839,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>960</v>
       </c>
@@ -15546,7 +15856,7 @@
         <v>1440</v>
       </c>
       <c r="F453" s="1">
-        <v>36.8</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="G453" s="1">
         <v>84.5</v>
@@ -15555,7 +15865,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>962</v>
       </c>
@@ -15572,7 +15882,7 @@
         <v>1598</v>
       </c>
       <c r="F454" s="1">
-        <v>40.8</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="G454" s="1">
         <v>44.4</v>
@@ -15581,7 +15891,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>964</v>
       </c>
@@ -15601,13 +15911,13 @@
         <v>59.9</v>
       </c>
       <c r="G455" s="1">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="H455" s="1">
         <v>275</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>966</v>
       </c>
@@ -15618,13 +15928,13 @@
         <v>25</v>
       </c>
       <c r="D456" s="1">
-        <v>134.3</v>
+        <v>134.30000000000001</v>
       </c>
       <c r="E456" s="1">
         <v>44453.3</v>
       </c>
       <c r="F456" s="1">
-        <v>1136.1</v>
+        <v>1136.0999999999999</v>
       </c>
       <c r="G456" s="1">
         <v>9.5</v>
@@ -15633,7 +15943,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>968</v>
       </c>
@@ -15650,7 +15960,7 @@
         <v>168030.1</v>
       </c>
       <c r="F457" s="1">
-        <v>4294.4</v>
+        <v>4294.3999999999996</v>
       </c>
       <c r="G457" s="1">
         <v>53.2</v>
@@ -15659,7 +15969,7 @@
         <v>2100.4</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>970</v>
       </c>
@@ -15682,10 +15992,10 @@
         <v>66.8</v>
       </c>
       <c r="H458" s="1">
-        <v>35.3</v>
-      </c>
-    </row>
-    <row r="459">
+        <v>35.299999999999997</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>972</v>
       </c>
@@ -15711,7 +16021,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>974</v>
       </c>
@@ -15737,7 +16047,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>976</v>
       </c>
@@ -15763,7 +16073,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>978</v>
       </c>
@@ -15780,7 +16090,7 @@
         <v>3030</v>
       </c>
       <c r="F462" s="1">
-        <v>77.4</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="G462" s="1">
         <v>13.5</v>
@@ -15789,7 +16099,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>981</v>
       </c>
@@ -15800,7 +16110,7 @@
         <v>93</v>
       </c>
       <c r="D463" s="1">
-        <v>17.1</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E463" s="1">
         <v>625.9</v>
@@ -15815,7 +16125,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>983</v>
       </c>
@@ -15841,7 +16151,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>985</v>
       </c>
@@ -15867,7 +16177,7 @@
         <v>43815.6</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>987</v>
       </c>
@@ -15893,7 +16203,7 @@
         <v>77.3</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>989</v>
       </c>
@@ -15910,7 +16220,7 @@
         <v>10109.4</v>
       </c>
       <c r="F467" s="1">
-        <v>258.4</v>
+        <v>258.39999999999998</v>
       </c>
       <c r="G467" s="1">
         <v>27.1</v>
@@ -15919,7 +16229,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>991</v>
       </c>
@@ -15939,13 +16249,13 @@
         <v>20.5</v>
       </c>
       <c r="G468" s="1">
-        <v>69.6</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H468" s="1">
         <v>53.6</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>993</v>
       </c>
@@ -15965,13 +16275,13 @@
         <v>21.3</v>
       </c>
       <c r="G469" s="1">
-        <v>68.1</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="H469" s="1">
         <v>468</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>995</v>
       </c>
@@ -15982,7 +16292,7 @@
         <v>120</v>
       </c>
       <c r="D470" s="1">
-        <v>75.4</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="E470" s="1">
         <v>46823.4</v>
@@ -15997,7 +16307,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>997</v>
       </c>
@@ -16023,7 +16333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>999</v>
       </c>
@@ -16049,7 +16359,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>1001</v>
       </c>
@@ -16075,7 +16385,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>1003</v>
       </c>
@@ -16101,7 +16411,7 @@
         <v>3250</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>1005</v>
       </c>
@@ -16121,13 +16431,13 @@
         <v>14.8</v>
       </c>
       <c r="G475" s="1">
-        <v>75.4</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="H475" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>1007</v>
       </c>
@@ -16153,7 +16463,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>1009</v>
       </c>
@@ -16179,7 +16489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>1011</v>
       </c>
@@ -16205,7 +16515,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>1013</v>
       </c>
@@ -16216,7 +16526,7 @@
         <v>36</v>
       </c>
       <c r="D479" s="1">
-        <v>81.4</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="E479" s="1">
         <v>773.3</v>
@@ -16231,7 +16541,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>1015</v>
       </c>
@@ -16257,7 +16567,7 @@
         <v>605.9</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>1017</v>
       </c>
@@ -16283,7 +16593,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>1019</v>
       </c>
@@ -16309,7 +16619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>1021</v>
       </c>
@@ -16326,7 +16636,7 @@
         <v>1577.9</v>
       </c>
       <c r="F483" s="1">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="G483" s="1">
         <v>25.3</v>
@@ -16335,7 +16645,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>1023</v>
       </c>
@@ -16361,7 +16671,7 @@
         <v>474.6</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>1025</v>
       </c>
@@ -16387,7 +16697,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>1027</v>
       </c>
@@ -16401,7 +16711,7 @@
         <v>15.38</v>
       </c>
       <c r="E486" s="1">
-        <v>8612.8</v>
+        <v>8612.7999999999993</v>
       </c>
       <c r="F486" s="1">
         <v>220.1</v>
@@ -16413,7 +16723,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>1029</v>
       </c>
@@ -16427,7 +16737,7 @@
         <v>10.64</v>
       </c>
       <c r="E487" s="1">
-        <v>4112.4</v>
+        <v>4112.3999999999996</v>
       </c>
       <c r="F487" s="1">
         <v>105.1</v>
@@ -16439,7 +16749,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>1031</v>
       </c>
@@ -16450,7 +16760,7 @@
         <v>74</v>
       </c>
       <c r="D488" s="1">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="E488" s="1">
         <v>1123.3</v>
@@ -16465,7 +16775,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>1033</v>
       </c>
@@ -16491,7 +16801,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>1035</v>
       </c>
@@ -16511,13 +16821,13 @@
         <v>190.4</v>
       </c>
       <c r="G490" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H490" s="1">
         <v>130</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>1037</v>
       </c>
@@ -16531,10 +16841,10 @@
         <v>182.8</v>
       </c>
       <c r="E491" s="1">
-        <v>21570.4</v>
+        <v>21570.400000000001</v>
       </c>
       <c r="F491" s="1">
-        <v>551.3</v>
+        <v>551.29999999999995</v>
       </c>
       <c r="G491" s="1">
         <v>23.7</v>
@@ -16543,7 +16853,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>1039</v>
       </c>
@@ -16569,7 +16879,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>1041</v>
       </c>
@@ -16586,16 +16896,16 @@
         <v>45072.9</v>
       </c>
       <c r="F493" s="1">
-        <v>1151.9</v>
+        <v>1151.9000000000001</v>
       </c>
       <c r="G493" s="1">
-        <v>20.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="H493" s="1">
         <v>261.3</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>1043</v>
       </c>
@@ -16606,7 +16916,7 @@
         <v>120</v>
       </c>
       <c r="D494" s="1">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="E494" s="1">
         <v>7909.7</v>
@@ -16621,7 +16931,7 @@
         <v>218.5</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>1045</v>
       </c>
@@ -16647,7 +16957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>1047</v>
       </c>
@@ -16664,7 +16974,7 @@
         <v>2920.5</v>
       </c>
       <c r="F496" s="1">
-        <v>74.6</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="G496" s="1">
         <v>41</v>
@@ -16673,7 +16983,7 @@
         <v>244.8</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>1049</v>
       </c>
@@ -16690,7 +17000,7 @@
         <v>11584.7</v>
       </c>
       <c r="F497" s="1">
-        <v>296.1</v>
+        <v>296.10000000000002</v>
       </c>
       <c r="G497" s="1">
         <v>23.2</v>
@@ -16699,7 +17009,7 @@
         <v>280.5</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>1051</v>
       </c>
@@ -16725,7 +17035,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>1053</v>
       </c>
@@ -16739,7 +17049,7 @@
         <v>73.5</v>
       </c>
       <c r="E499" s="1">
-        <v>1041.9</v>
+        <v>1041.9000000000001</v>
       </c>
       <c r="F499" s="1">
         <v>26.6</v>
@@ -16751,7 +17061,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>1055</v>
       </c>
@@ -16771,13 +17081,13 @@
         <v>52.7</v>
       </c>
       <c r="G500" s="1">
-        <v>65.1</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="H500" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>1057</v>
       </c>
@@ -16794,7 +17104,7 @@
         <v>41921</v>
       </c>
       <c r="F501" s="1">
-        <v>1071.4</v>
+        <v>1071.4000000000001</v>
       </c>
       <c r="G501" s="1">
         <v>26.5</v>
@@ -16803,7 +17113,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>1059</v>
       </c>
@@ -16829,7 +17139,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>1061</v>
       </c>
@@ -16855,7 +17165,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>1063</v>
       </c>
@@ -16869,7 +17179,7 @@
         <v>13992.5</v>
       </c>
       <c r="E504" s="1">
-        <v>26460.8</v>
+        <v>26460.799999999999</v>
       </c>
       <c r="F504" s="1">
         <v>676.3</v>
@@ -16881,7 +17191,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>1065</v>
       </c>
@@ -16907,7 +17217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>1067</v>
       </c>
@@ -16933,7 +17243,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>1069</v>
       </c>
@@ -16959,7 +17269,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>1071</v>
       </c>
@@ -16985,7 +17295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>1073</v>
       </c>
@@ -17011,7 +17321,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>1075</v>
       </c>
@@ -17037,7 +17347,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>1077</v>
       </c>
@@ -17063,7 +17373,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>1078</v>
       </c>
@@ -17089,7 +17399,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>1080</v>
       </c>
@@ -17115,7 +17425,7 @@
         <v>322.5</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>1082</v>
       </c>
@@ -17126,22 +17436,22 @@
         <v>99</v>
       </c>
       <c r="D514" s="1">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="E514" s="1">
         <v>11115</v>
       </c>
       <c r="F514" s="1">
-        <v>284.1</v>
+        <v>284.10000000000002</v>
       </c>
       <c r="G514" s="1">
-        <v>40.7</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="H514" s="1">
         <v>4500</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>1084</v>
       </c>
@@ -17167,7 +17477,7 @@
         <v>255.6</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>1086</v>
       </c>
@@ -17181,7 +17491,7 @@
         <v>15.28</v>
       </c>
       <c r="E516" s="1">
-        <v>16502.4</v>
+        <v>16502.400000000001</v>
       </c>
       <c r="F516" s="1">
         <v>421.8</v>
@@ -17193,7 +17503,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>1088</v>
       </c>
@@ -17210,7 +17520,7 @@
         <v>3054.1</v>
       </c>
       <c r="F517" s="1">
-        <v>78.1</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="G517" s="1">
         <v>25.8</v>
@@ -17219,7 +17529,7 @@
         <v>228.6</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>1090</v>
       </c>
@@ -17242,10 +17552,10 @@
         <v>44.1</v>
       </c>
       <c r="H518" s="1">
-        <v>161.8</v>
-      </c>
-    </row>
-    <row r="519">
+        <v>161.80000000000001</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>1092</v>
       </c>
@@ -17271,7 +17581,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>1094</v>
       </c>
@@ -17297,7 +17607,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>1096</v>
       </c>
@@ -17323,7 +17633,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>1098</v>
       </c>
@@ -17349,7 +17659,7 @@
         <v>1926.8</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>1100</v>
       </c>
@@ -17366,7 +17676,7 @@
         <v>396060</v>
       </c>
       <c r="F523" s="1">
-        <v>10122.2</v>
+        <v>10122.200000000001</v>
       </c>
       <c r="G523" s="1">
         <v>50.2</v>
@@ -17375,7 +17685,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>1102</v>
       </c>
@@ -17401,7 +17711,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>1104</v>
       </c>
@@ -17427,7 +17737,7 @@
         <v>100.1</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>1106</v>
       </c>
@@ -17453,7 +17763,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>1108</v>
       </c>
@@ -17473,13 +17783,13 @@
         <v>2126.4</v>
       </c>
       <c r="G527" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H527" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>1110</v>
       </c>
@@ -17496,16 +17806,16 @@
         <v>44973</v>
       </c>
       <c r="F528" s="1">
-        <v>1149.4</v>
+        <v>1149.4000000000001</v>
       </c>
       <c r="G528" s="1">
-        <v>39.8</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="H528" s="1">
         <v>46.8</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>1112</v>
       </c>
@@ -17531,7 +17841,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>1114</v>
       </c>
@@ -17557,7 +17867,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>1116</v>
       </c>
@@ -17568,7 +17878,7 @@
         <v>10</v>
       </c>
       <c r="D531" s="1">
-        <v>131.2</v>
+        <v>131.19999999999999</v>
       </c>
       <c r="E531" s="1">
         <v>10496</v>
@@ -17583,7 +17893,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>1118</v>
       </c>
@@ -17603,13 +17913,13 @@
         <v>121.3</v>
       </c>
       <c r="G532" s="1">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="H532" s="1">
         <v>750</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>1120</v>
       </c>
@@ -17620,7 +17930,7 @@
         <v>13</v>
       </c>
       <c r="D533" s="1">
-        <v>9.3</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="E533" s="1">
         <v>390.6</v>
@@ -17635,7 +17945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>1122</v>
       </c>
@@ -17661,7 +17971,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>1124</v>
       </c>
@@ -17687,7 +17997,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>1126</v>
       </c>
@@ -17707,13 +18017,13 @@
         <v>192.3</v>
       </c>
       <c r="G536" s="1">
-        <v>37.8</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="H536" s="1">
         <v>3500</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>1128</v>
       </c>
@@ -17739,7 +18049,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>1130</v>
       </c>
@@ -17765,7 +18075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>1132</v>
       </c>
@@ -17791,7 +18101,7 @@
         <v>9915.9</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>1134</v>
       </c>
@@ -17802,7 +18112,7 @@
         <v>99</v>
       </c>
       <c r="D540" s="1">
-        <v>40.38</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="E540" s="1">
         <v>1009.5</v>
@@ -17817,7 +18127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>1136</v>
       </c>
@@ -17843,7 +18153,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>1138</v>
       </c>
@@ -17863,13 +18173,13 @@
         <v>50.3</v>
       </c>
       <c r="G542" s="1">
-        <v>38.7</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="H542" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>1140</v>
       </c>
@@ -17895,7 +18205,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>1142</v>
       </c>
@@ -17921,7 +18231,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>1144</v>
       </c>
@@ -17947,7 +18257,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>1146</v>
       </c>
@@ -17964,7 +18274,7 @@
         <v>11720.8</v>
       </c>
       <c r="F546" s="1">
-        <v>299.6</v>
+        <v>299.60000000000002</v>
       </c>
       <c r="G546" s="1">
         <v>47.2</v>
@@ -17973,7 +18283,7 @@
         <v>335.5</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>1148</v>
       </c>
@@ -17987,7 +18297,7 @@
         <v>26.86</v>
       </c>
       <c r="E547" s="1">
-        <v>1128.1</v>
+        <v>1128.0999999999999</v>
       </c>
       <c r="F547" s="1">
         <v>28.8</v>
@@ -17999,7 +18309,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>1150</v>
       </c>
@@ -18013,7 +18323,7 @@
         <v>453.75</v>
       </c>
       <c r="E548" s="1">
-        <v>53088.8</v>
+        <v>53088.800000000003</v>
       </c>
       <c r="F548" s="1">
         <v>1356.8</v>
@@ -18025,7 +18335,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>1152</v>
       </c>
@@ -18051,7 +18361,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>1154</v>
       </c>
@@ -18071,13 +18381,13 @@
         <v>5954.1</v>
       </c>
       <c r="G550" s="1">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H550" s="1">
         <v>8447.1</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>1156</v>
       </c>
@@ -18100,10 +18410,10 @@
         <v>59</v>
       </c>
       <c r="H551" s="1">
-        <v>149.8</v>
-      </c>
-    </row>
-    <row r="552">
+        <v>149.80000000000001</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>1158</v>
       </c>
@@ -18120,7 +18430,7 @@
         <v>10598.1</v>
       </c>
       <c r="F552" s="1">
-        <v>270.9</v>
+        <v>270.89999999999998</v>
       </c>
       <c r="G552" s="1">
         <v>31</v>
@@ -18129,7 +18439,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>1160</v>
       </c>
@@ -18143,7 +18453,7 @@
         <v>23.32</v>
       </c>
       <c r="E553" s="1">
-        <v>1163.1</v>
+        <v>1163.0999999999999</v>
       </c>
       <c r="F553" s="1">
         <v>29.7</v>
@@ -18155,7 +18465,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>1162</v>
       </c>
@@ -18169,7 +18479,7 @@
         <v>83.15</v>
       </c>
       <c r="E554" s="1">
-        <v>20115.6</v>
+        <v>20115.599999999999</v>
       </c>
       <c r="F554" s="1">
         <v>514.1</v>
@@ -18181,7 +18491,7 @@
         <v>241.9</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>1164</v>
       </c>
@@ -18201,13 +18511,13 @@
         <v>380.3</v>
       </c>
       <c r="G555" s="1">
-        <v>36.3</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="H555" s="1">
         <v>355</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>1166</v>
       </c>
@@ -18233,7 +18543,7 @@
         <v>852.5</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>1168</v>
       </c>
@@ -18253,13 +18563,13 @@
         <v>42</v>
       </c>
       <c r="G557" s="1">
-        <v>78.4</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="H557" s="1">
         <v>263.2</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>1170</v>
       </c>
@@ -18285,7 +18595,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>1172</v>
       </c>
@@ -18311,7 +18621,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>1174</v>
       </c>
@@ -18337,7 +18647,7 @@
         <v>300.5</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>1176</v>
       </c>
@@ -18351,7 +18661,7 @@
         <v>62</v>
       </c>
       <c r="E561" s="1">
-        <v>1041.6</v>
+        <v>1041.5999999999999</v>
       </c>
       <c r="F561" s="1">
         <v>26.6</v>
@@ -18363,7 +18673,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>1178</v>
       </c>
@@ -18383,13 +18693,13 @@
         <v>30.4</v>
       </c>
       <c r="G562" s="1">
-        <v>39.2</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H562" s="1">
         <v>250</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>1180</v>
       </c>
@@ -18406,7 +18716,7 @@
         <v>2529.6</v>
       </c>
       <c r="F563" s="1">
-        <v>64.6</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="G563" s="1">
         <v>42</v>
@@ -18415,7 +18725,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>1182</v>
       </c>
@@ -18429,7 +18739,7 @@
         <v>7.47</v>
       </c>
       <c r="E564" s="1">
-        <v>1305.4</v>
+        <v>1305.4000000000001</v>
       </c>
       <c r="F564" s="1">
         <v>33.4</v>
@@ -18441,7 +18751,7 @@
         <v>174.8</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>1184</v>
       </c>
@@ -18461,13 +18771,13 @@
         <v>2878.9</v>
       </c>
       <c r="G565" s="1">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="H565" s="1">
-        <v>4693.6</v>
-      </c>
-    </row>
-    <row r="566">
+        <v>4693.6000000000004</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>1186</v>
       </c>
@@ -18487,13 +18797,13 @@
         <v>388.5</v>
       </c>
       <c r="G566" s="1">
-        <v>37.3</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="H566" s="1">
         <v>5000</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>1188</v>
       </c>
@@ -18519,7 +18829,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>1190</v>
       </c>
@@ -18545,7 +18855,7 @@
         <v>165.2</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>1192</v>
       </c>
@@ -18559,7 +18869,7 @@
         <v>28.48</v>
       </c>
       <c r="E569" s="1">
-        <v>4784.6</v>
+        <v>4784.6000000000004</v>
       </c>
       <c r="F569" s="1">
         <v>122.3</v>
@@ -18571,7 +18881,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>1195</v>
       </c>
@@ -18597,7 +18907,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>1197</v>
       </c>
@@ -18623,7 +18933,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>1199</v>
       </c>
@@ -18649,7 +18959,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>1201</v>
       </c>
@@ -18666,16 +18976,16 @@
         <v>5605</v>
       </c>
       <c r="F573" s="1">
-        <v>143.2</v>
+        <v>143.19999999999999</v>
       </c>
       <c r="G573" s="1">
-        <v>40.2</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="H573" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>1203</v>
       </c>
@@ -18701,7 +19011,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>1205</v>
       </c>
@@ -18727,7 +19037,7 @@
         <v>87.1</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>1207</v>
       </c>
@@ -18753,7 +19063,7 @@
         <v>945.6</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>1209</v>
       </c>
@@ -18764,7 +19074,7 @@
         <v>253</v>
       </c>
       <c r="D577" s="1">
-        <v>19.85</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="E577" s="1">
         <v>1414.3</v>
@@ -18779,7 +19089,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>1211</v>
       </c>
@@ -18805,7 +19115,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>1213</v>
       </c>
@@ -18825,13 +19135,13 @@
         <v>245.3</v>
       </c>
       <c r="G579" s="1">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="H579" s="1">
-        <v>71.4</v>
-      </c>
-    </row>
-    <row r="580">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>1215</v>
       </c>
@@ -18857,7 +19167,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>1217</v>
       </c>
@@ -18871,7 +19181,7 @@
         <v>7.52</v>
       </c>
       <c r="E581" s="1">
-        <v>552.7</v>
+        <v>552.70000000000005</v>
       </c>
       <c r="F581" s="1">
         <v>14.1</v>
@@ -18883,7 +19193,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>1219</v>
       </c>
@@ -18903,13 +19213,13 @@
         <v>78.5</v>
       </c>
       <c r="G582" s="1">
-        <v>33.3</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="H582" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>1221</v>
       </c>
@@ -18926,7 +19236,7 @@
         <v>2840.1</v>
       </c>
       <c r="F583" s="1">
-        <v>72.6</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="G583" s="1">
         <v>28.6</v>
@@ -18935,7 +19245,7 @@
         <v>103.2</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>1223</v>
       </c>
@@ -18961,7 +19271,7 @@
         <v>369.3</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>1225</v>
       </c>
@@ -18987,7 +19297,7 @@
         <v>175.7</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>1227</v>
       </c>
@@ -19013,7 +19323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="587">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>1229</v>
       </c>
@@ -19039,7 +19349,7 @@
         <v>813.6</v>
       </c>
     </row>
-    <row r="588">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>1231</v>
       </c>
@@ -19059,13 +19369,13 @@
         <v>43.3</v>
       </c>
       <c r="G588" s="1">
-        <v>33.8</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="H588" s="1">
         <v>155</v>
       </c>
     </row>
-    <row r="589">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>1233</v>
       </c>
@@ -19082,7 +19392,7 @@
         <v>11850</v>
       </c>
       <c r="F589" s="1">
-        <v>302.9</v>
+        <v>302.89999999999998</v>
       </c>
       <c r="G589" s="1">
         <v>50</v>
@@ -19091,7 +19401,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="590">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>1235</v>
       </c>
@@ -19117,7 +19427,7 @@
         <v>3063.2</v>
       </c>
     </row>
-    <row r="591">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>1237</v>
       </c>
@@ -19128,22 +19438,60 @@
         <v>234</v>
       </c>
       <c r="D591" s="1">
-        <v>34.48</v>
+        <v>34.479999999999997</v>
       </c>
       <c r="E591" s="1">
-        <v>20456.6</v>
+        <v>20456.599999999999</v>
       </c>
       <c r="F591" s="1">
-        <v>522.8</v>
+        <v>522.79999999999995</v>
       </c>
       <c r="G591" s="1">
         <v>45.7</v>
       </c>
       <c r="H591" s="1">
-        <v>593.3</v>
-      </c>
+        <v>593.29999999999995</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A592" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D592">
+        <v>105</v>
+      </c>
+      <c r="E592">
+        <v>16280</v>
+      </c>
+      <c r="F592">
+        <v>378</v>
+      </c>
+      <c r="G592">
+        <v>29.03</v>
+      </c>
+      <c r="H592">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A599" s="1"/>
+      <c r="B599" s="1"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1"/>
+      <c r="E599" s="1"/>
+      <c r="F599" s="1"/>
+      <c r="G599" s="1"/>
+      <c r="H599" s="1"/>
+      <c r="I599" s="1"/>
     </row>
   </sheetData>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/temelozet.xlsx
+++ b/temelozet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1287">
   <si>
     <t>Kod</t>
   </si>
@@ -3745,16 +3745,159 @@
   </si>
   <si>
     <t>Endüstriyel Makine / Teknoloji</t>
+  </si>
+  <si>
+    <t>MARMR</t>
+  </si>
+  <si>
+    <t>Marmara Holding A.Ş.</t>
+  </si>
+  <si>
+    <t>ECOGR</t>
+  </si>
+  <si>
+    <t>Ecogreen Enerji Holding A.Ş.</t>
+  </si>
+  <si>
+    <t>Enerji</t>
+  </si>
+  <si>
+    <t>VAKFA</t>
+  </si>
+  <si>
+    <t>Vakıf Faktoring A.Ş.</t>
+  </si>
+  <si>
+    <t>PAHOL</t>
+  </si>
+  <si>
+    <t>Pasifik Holding A.Ş.</t>
+  </si>
+  <si>
+    <t>ZERGY</t>
+  </si>
+  <si>
+    <t>Zeray Gayrimenkul Yatırım Ortaklığı A.Ş.</t>
+  </si>
+  <si>
+    <t>ARFYE</t>
+  </si>
+  <si>
+    <t>Arf Bio Yenilenebilir Enerji Üretim A.Ş.</t>
+  </si>
+  <si>
+    <t>Yenilenebilir enerji</t>
+  </si>
+  <si>
+    <t>MEYSU</t>
+  </si>
+  <si>
+    <t>Meysu Gıda San. ve Tic. A.Ş.</t>
+  </si>
+  <si>
+    <t>ZGYO</t>
+  </si>
+  <si>
+    <t>FRMPL</t>
+  </si>
+  <si>
+    <t>UCAYM</t>
+  </si>
+  <si>
+    <t>NETCD</t>
+  </si>
+  <si>
+    <t>AKHAN</t>
+  </si>
+  <si>
+    <t>BESTE</t>
+  </si>
+  <si>
+    <t>ATATR</t>
+  </si>
+  <si>
+    <t>EMPAE</t>
+  </si>
+  <si>
+    <t>SVGYO</t>
+  </si>
+  <si>
+    <t>GENKM</t>
+  </si>
+  <si>
+    <t>LXGYO</t>
+  </si>
+  <si>
+    <t>MCARD</t>
+  </si>
+  <si>
+    <t>AAGYO</t>
+  </si>
+  <si>
+    <t>Kimya</t>
+  </si>
+  <si>
+    <t>Formül Plastik ve Metal Sanayi A.Ş.</t>
+  </si>
+  <si>
+    <t>Sanayi</t>
+  </si>
+  <si>
+    <t>Üçay Mühendislik Enerji A.Ş.</t>
+  </si>
+  <si>
+    <t>Netcad Yazılım A.Ş.</t>
+  </si>
+  <si>
+    <t>Yazılım</t>
+  </si>
+  <si>
+    <t>Akhan Un Fabrikası A.Ş.</t>
+  </si>
+  <si>
+    <t>Best Brands Grup Enerji A.Ş.</t>
+  </si>
+  <si>
+    <t>Ata Turizm A.Ş.</t>
+  </si>
+  <si>
+    <t>Empa Elektronik San. ve Tic. A.Ş.</t>
+  </si>
+  <si>
+    <t>Elektronik</t>
+  </si>
+  <si>
+    <t>Gentaş Kimya A.Ş.</t>
+  </si>
+  <si>
+    <t>Luxera GYO</t>
+  </si>
+  <si>
+    <t>MetropolCard (Metropal)</t>
+  </si>
+  <si>
+    <t>Fintech</t>
+  </si>
+  <si>
+    <t>210.5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3766,6 +3909,43 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
     </font>
@@ -3787,16 +3967,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4075,10 +4282,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I599"/>
+  <dimension ref="A1:I628"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.44140625" customWidth="1"/>
     <col min="4" max="4" width="15.21875" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -4789,7 +4996,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
@@ -19479,19 +19686,678 @@
         <v>155</v>
       </c>
     </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A593" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D593" s="4">
+        <v>2.27</v>
+      </c>
+      <c r="E593">
+        <v>6850</v>
+      </c>
+      <c r="F593" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="G593">
+        <v>21.62</v>
+      </c>
+      <c r="H593">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A594" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D594">
+        <v>33.96</v>
+      </c>
+      <c r="E594">
+        <v>18340</v>
+      </c>
+      <c r="F594">
+        <v>416</v>
+      </c>
+      <c r="G594">
+        <v>20.36</v>
+      </c>
+      <c r="H594">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A595" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D595">
+        <v>11.71</v>
+      </c>
+      <c r="E595">
+        <v>1054</v>
+      </c>
+      <c r="F595">
+        <v>23.9</v>
+      </c>
+      <c r="G595">
+        <v>24.99</v>
+      </c>
+      <c r="H595">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A596" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B596" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D596">
+        <v>1.52</v>
+      </c>
+      <c r="E596">
+        <v>30400</v>
+      </c>
+      <c r="F596">
+        <v>690</v>
+      </c>
+      <c r="G596">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="H596">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A597" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B597" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C597" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D597">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="E597">
+        <v>12000</v>
+      </c>
+      <c r="F597">
+        <v>272</v>
+      </c>
+      <c r="G597">
+        <v>25.04</v>
+      </c>
+      <c r="H597">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A598" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B598" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D598">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="E598">
+        <v>23250</v>
+      </c>
+      <c r="F598">
+        <v>528</v>
+      </c>
+      <c r="G598">
+        <v>28.42</v>
+      </c>
+      <c r="H598">
+        <v>1196</v>
+      </c>
+    </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A599" s="1"/>
-      <c r="B599" s="1"/>
-      <c r="C599" s="1"/>
-      <c r="D599" s="1"/>
-      <c r="E599" s="1"/>
-      <c r="F599" s="1"/>
-      <c r="G599" s="1"/>
-      <c r="H599" s="1"/>
+      <c r="A599" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B599" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D599" s="1">
+        <v>13.27</v>
+      </c>
+      <c r="E599" s="1">
+        <v>12500</v>
+      </c>
+      <c r="F599" s="1">
+        <v>284</v>
+      </c>
+      <c r="G599" s="1">
+        <v>20.11</v>
+      </c>
+      <c r="H599" s="1">
+        <v>870</v>
+      </c>
       <c r="I599" s="1"/>
     </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A600" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B600" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C600" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D600" s="9">
+        <v>23.26</v>
+      </c>
+      <c r="E600">
+        <v>4896</v>
+      </c>
+      <c r="F600" s="11">
+        <v>155</v>
+      </c>
+      <c r="G600" s="9">
+        <v>23</v>
+      </c>
+      <c r="H600" s="14" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A601" s="7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B601" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C601" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D601" s="9">
+        <v>38.9</v>
+      </c>
+      <c r="E601">
+        <v>1560</v>
+      </c>
+      <c r="F601" s="11">
+        <v>50</v>
+      </c>
+      <c r="G601" s="9">
+        <v>25</v>
+      </c>
+      <c r="H601" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A602" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B602" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C602" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D602" s="9">
+        <v>32.5</v>
+      </c>
+      <c r="E602">
+        <v>1950</v>
+      </c>
+      <c r="F602" s="11">
+        <v>63</v>
+      </c>
+      <c r="G602" s="9">
+        <v>26</v>
+      </c>
+      <c r="H602" s="14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A603" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B603" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C603" s="8" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D603" s="9">
+        <v>74</v>
+      </c>
+      <c r="E603" s="1">
+        <v>7400</v>
+      </c>
+      <c r="F603" s="11">
+        <v>240</v>
+      </c>
+      <c r="G603" s="9">
+        <v>20</v>
+      </c>
+      <c r="H603" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A604" s="7" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B604" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C604" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D604" s="9">
+        <v>31.46</v>
+      </c>
+      <c r="E604">
+        <v>1720</v>
+      </c>
+      <c r="F604" s="11">
+        <v>55</v>
+      </c>
+      <c r="G604" s="9">
+        <v>20</v>
+      </c>
+      <c r="H604" s="14">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A605" s="7" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B605" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C605" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D605" s="9">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="E605">
+        <v>800</v>
+      </c>
+      <c r="F605" s="11">
+        <v>26</v>
+      </c>
+      <c r="G605" s="9">
+        <v>25</v>
+      </c>
+      <c r="H605" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A606" s="7" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B606" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C606" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D606" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="E606">
+        <v>1000</v>
+      </c>
+      <c r="F606" s="11">
+        <v>32</v>
+      </c>
+      <c r="G606" s="9">
+        <v>20</v>
+      </c>
+      <c r="H606" s="14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A607" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B607" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C607" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D607" s="9">
+        <v>37</v>
+      </c>
+      <c r="E607">
+        <v>3000</v>
+      </c>
+      <c r="F607" s="11">
+        <v>97</v>
+      </c>
+      <c r="G607" s="9">
+        <v>30</v>
+      </c>
+      <c r="H607" s="14">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A608" s="7" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B608" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C608" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D608" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="E608">
+        <v>3200</v>
+      </c>
+      <c r="F608" s="11">
+        <v>103</v>
+      </c>
+      <c r="G608" s="9">
+        <v>30</v>
+      </c>
+      <c r="H608" s="14">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A609" s="7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B609" s="8" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C609" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D609" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="E609">
+        <v>5300</v>
+      </c>
+      <c r="F609" s="11">
+        <v>171</v>
+      </c>
+      <c r="G609" s="9">
+        <v>21</v>
+      </c>
+      <c r="H609" s="14">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A610" s="7" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B610" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C610" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D610" s="9">
+        <v>46190</v>
+      </c>
+      <c r="E610">
+        <v>2200</v>
+      </c>
+      <c r="F610" s="11">
+        <v>71</v>
+      </c>
+      <c r="G610" s="9">
+        <v>40</v>
+      </c>
+      <c r="H610" s="14">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A611" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B611" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C611" s="8" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D611" s="9">
+        <v>106</v>
+      </c>
+      <c r="E611">
+        <v>5000</v>
+      </c>
+      <c r="F611" s="11">
+        <v>161</v>
+      </c>
+      <c r="G611" s="9">
+        <v>12</v>
+      </c>
+      <c r="H611" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A612" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B612" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C612" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D612" s="9">
+        <v>5</v>
+      </c>
+      <c r="E612">
+        <v>4000</v>
+      </c>
+      <c r="F612" s="11">
+        <v>129</v>
+      </c>
+      <c r="G612" s="9">
+        <v>35</v>
+      </c>
+      <c r="H612" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A613" s="6"/>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A615" s="10"/>
+      <c r="B615" s="10"/>
+      <c r="C615" s="10"/>
+      <c r="D615" s="10"/>
+      <c r="E615" s="10"/>
+      <c r="F615" s="10"/>
+      <c r="G615" s="10"/>
+      <c r="H615" s="10"/>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A616" s="11"/>
+      <c r="B616" s="11"/>
+      <c r="C616" s="11"/>
+      <c r="D616" s="11"/>
+      <c r="E616" s="12"/>
+      <c r="F616" s="11"/>
+      <c r="G616" s="13"/>
+      <c r="H616" s="11"/>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A617" s="11"/>
+      <c r="B617" s="11"/>
+      <c r="C617" s="11"/>
+      <c r="D617" s="11"/>
+      <c r="E617" s="11"/>
+      <c r="F617" s="11"/>
+      <c r="G617" s="11"/>
+      <c r="H617" s="11"/>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A618" s="11"/>
+      <c r="B618" s="11"/>
+      <c r="C618" s="11"/>
+      <c r="D618" s="11"/>
+      <c r="E618" s="11"/>
+      <c r="F618" s="11"/>
+      <c r="G618" s="13"/>
+      <c r="H618" s="11"/>
+    </row>
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A619" s="11"/>
+      <c r="B619" s="11"/>
+      <c r="C619" s="11"/>
+      <c r="D619" s="11"/>
+      <c r="E619" s="11"/>
+      <c r="F619" s="11"/>
+      <c r="G619" s="11"/>
+      <c r="H619" s="11"/>
+    </row>
+    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A620" s="11"/>
+      <c r="B620" s="11"/>
+      <c r="C620" s="11"/>
+      <c r="D620" s="11"/>
+      <c r="E620" s="11"/>
+      <c r="F620" s="11"/>
+      <c r="G620" s="11"/>
+      <c r="H620" s="11"/>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A621" s="11"/>
+      <c r="B621" s="11"/>
+      <c r="C621" s="11"/>
+      <c r="D621" s="11"/>
+      <c r="E621" s="11"/>
+      <c r="F621" s="11"/>
+      <c r="G621" s="11"/>
+      <c r="H621" s="11"/>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A622" s="11"/>
+      <c r="B622" s="11"/>
+      <c r="C622" s="11"/>
+      <c r="D622" s="11"/>
+      <c r="E622" s="11"/>
+      <c r="F622" s="11"/>
+      <c r="G622" s="11"/>
+      <c r="H622" s="11"/>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A623" s="11"/>
+      <c r="B623" s="11"/>
+      <c r="C623" s="11"/>
+      <c r="D623" s="11"/>
+      <c r="E623" s="11"/>
+      <c r="F623" s="11"/>
+      <c r="G623" s="11"/>
+      <c r="H623" s="11"/>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A624" s="11"/>
+      <c r="B624" s="11"/>
+      <c r="C624" s="11"/>
+      <c r="D624" s="11"/>
+      <c r="E624" s="11"/>
+      <c r="F624" s="11"/>
+      <c r="G624" s="11"/>
+      <c r="H624" s="11"/>
+    </row>
+    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A625" s="11"/>
+      <c r="B625" s="11"/>
+      <c r="C625" s="11"/>
+      <c r="D625" s="11"/>
+      <c r="E625" s="11"/>
+      <c r="F625" s="11"/>
+      <c r="G625" s="11"/>
+      <c r="H625" s="11"/>
+    </row>
+    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A626" s="11"/>
+      <c r="B626" s="11"/>
+      <c r="C626" s="11"/>
+      <c r="D626" s="11"/>
+      <c r="E626" s="11"/>
+      <c r="F626" s="11"/>
+      <c r="G626" s="11"/>
+      <c r="H626" s="11"/>
+    </row>
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A627" s="11"/>
+      <c r="B627" s="11"/>
+      <c r="C627" s="11"/>
+      <c r="D627" s="11"/>
+      <c r="E627" s="11"/>
+      <c r="F627" s="11"/>
+      <c r="G627" s="11"/>
+      <c r="H627" s="11"/>
+    </row>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A628" s="11"/>
+      <c r="B628" s="11"/>
+      <c r="C628" s="11"/>
+      <c r="D628" s="11"/>
+      <c r="E628" s="11"/>
+      <c r="F628" s="11"/>
+      <c r="G628" s="11"/>
+      <c r="H628" s="11"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B596" r:id="rId1" tooltip="Pasifik Holding A.Ş." display="https://halkarz.com/pasifik-holding-a-s/"/>
+    <hyperlink ref="B597" r:id="rId2" tooltip="Zeray Gayrimenkul Yatırım Ortaklığı A.Ş." display="https://halkarz.com/zeray-gayrimenkul-yatirim-ortakligi-a-s/"/>
+    <hyperlink ref="B598" r:id="rId3" tooltip="Arf Bio Yenilenebilir Enerji Üretim A.Ş." display="https://halkarz.com/arf-bio-yenilenebilir-enerji-uretim-a-s/"/>
+    <hyperlink ref="B599" r:id="rId4" tooltip="Meysu Gıda San. ve Tic. A.Ş." display="https://halkarz.com/meysu-gida-san-ve-tic-a-s/"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>